--- a/NUMEX_pre_RStudio/models_est.xlsx
+++ b/NUMEX_pre_RStudio/models_est.xlsx
@@ -1,2242 +1,2248 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\selene.baez\Downloads\NUMEX_preliminar\NUMEX_pre_RStudio\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="739">
-  <si>
-    <t xml:space="preserve">Modelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimates.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimates.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimates.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimates.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimates.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimates.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimates.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimates.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimates.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gof</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gof.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gof.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gof.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">term</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(Intercept)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUBN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUBNP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SD (Intercept Bloque)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SD (Observations)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Num.Obs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R2 Marg.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R2 Cond.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">statistic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">std.error</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Nmass | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.336***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.480)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.579)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.780</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.592)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.320*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.561)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nmass | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.393***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.314)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.629)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.259*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.739)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nmass | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.606***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.448)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.533*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.665)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.708)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.601)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nmass | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.812***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.287)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.192**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.386)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.909*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.366)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.369)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nmass | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.134***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.119)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.403*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.180)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.589+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.421)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.131)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.920</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nmass | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.434***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.699)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.989)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.308)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.947)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logNmass | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.728***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.030)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.036)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.082*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.034)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-54.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logNmass | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.849***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.070)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.141)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.093)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logNmass | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.442***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.039)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.058)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.061)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-26.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logNmass | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.168***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.032)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.043)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.041)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.071+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-52.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logNmass | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.648***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.065)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.201**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.078)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.062)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logNmass | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.338***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.064)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.091)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.121)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.087)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narea | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.920***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.075)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.108)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.120)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.250*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.115)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narea | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.892***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.112)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narea | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.272***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.161)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.231)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.247)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.209)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narea | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.882***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.260)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.410)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.380)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.389)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narea | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.136***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.170)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.702**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.222)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.214)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narea | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.484***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.102)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.144)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.191)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.138)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmass | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">478.002***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.864)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.637)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.819)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.718)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmass | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.372***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.884)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(15.767)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(10.429)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmass | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">489.936***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.460)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.649)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.054)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.353)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmass | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">472.530***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.366)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.836*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.124)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.157)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmass | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">438.175***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.416)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.459)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.373)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.301)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmass | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">444.044***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.317)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.780)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.429+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9.040)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.503)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carea | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.501***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.765)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.434)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.261)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carea | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.093***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.463)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.463*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.642)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.063*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.656)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.759)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carea | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.527***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.780)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.588)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8.078)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.856)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carea | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.985***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.549)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.612)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.209)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.324)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">393.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carea | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.582***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.939)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.687)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8.065)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.467)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carea | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.680***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.815)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.981)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.266)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.812)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLCCC | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.170***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.004)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.005)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-155.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLCCC |1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.043***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.018)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.037)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.024)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-16.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLCCC  | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.194***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-183.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLCCC  | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.158***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.017*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-219.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLCCC  | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.083***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.010)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-71.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLCCC  | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.096***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.015)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.039+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.021)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-45.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.650***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.066)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.068)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-14.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.793***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.155)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.103)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.079)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.094)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.100)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.099)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.157)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.263***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.149)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.151)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.182)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.119)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.168)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.223)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.077***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.446***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.076)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.096)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.178+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.233*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.067)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.134)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.088)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.257**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.081)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.092)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.098)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.085)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.883***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.090)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.143)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.132)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.315***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.135)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.183*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.082)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.111)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.249+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.585***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.086)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.122)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.162)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.043***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.117)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parea | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.081***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.011+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.018**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-170.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parea | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.087***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.022+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.033*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-27.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parea | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.221***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.056)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.174***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.047)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-34.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parea | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.033)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.048)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.049)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-38.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parea | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.027)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.044)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.093*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.035)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-29.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parea | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.080***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.016)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.023)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.022)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-35.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leaf N:P | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.474***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.600)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.188)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.331)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.223)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leaf N:P | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.867***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.675)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.186)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.953+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.198)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leaf N:P | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.015***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.948)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.175*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.897)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.308***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.953)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.939***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.810)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">203.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leaf N:P | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.224***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.132)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.582)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-11.021***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.492)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-16.982***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.508)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">279.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leaf N:P | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.046***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.615)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.648*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.036)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.420</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.453)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.056**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.961)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leaf N:P | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.652***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.117)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.580)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.090)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-11.345***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.513)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="739">
+  <si>
+    <t>Modelo</t>
+  </si>
+  <si>
+    <t>estimates</t>
+  </si>
+  <si>
+    <t>estimates.1</t>
+  </si>
+  <si>
+    <t>estimates.2</t>
+  </si>
+  <si>
+    <t>estimates.3</t>
+  </si>
+  <si>
+    <t>estimates.4</t>
+  </si>
+  <si>
+    <t>estimates.5</t>
+  </si>
+  <si>
+    <t>estimates.6</t>
+  </si>
+  <si>
+    <t>estimates.7</t>
+  </si>
+  <si>
+    <t>estimates.8</t>
+  </si>
+  <si>
+    <t>estimates.9</t>
+  </si>
+  <si>
+    <t>gof</t>
+  </si>
+  <si>
+    <t>gof.1</t>
+  </si>
+  <si>
+    <t>gof.2</t>
+  </si>
+  <si>
+    <t>gof.3</t>
+  </si>
+  <si>
+    <t>term</t>
+  </si>
+  <si>
+    <t>(Intercept)</t>
+  </si>
+  <si>
+    <t>SUBN</t>
+  </si>
+  <si>
+    <t>SUBNP</t>
+  </si>
+  <si>
+    <t>SUBP</t>
+  </si>
+  <si>
+    <t>SD (Intercept Bloque)</t>
+  </si>
+  <si>
+    <t>SD (Observations)</t>
+  </si>
+  <si>
+    <t>Num.Obs.</t>
+  </si>
+  <si>
+    <t>R2 Marg.</t>
+  </si>
+  <si>
+    <t>R2 Cond.</t>
+  </si>
+  <si>
+    <t>AIC</t>
+  </si>
+  <si>
+    <t>statistic</t>
+  </si>
+  <si>
+    <t>estimate</t>
+  </si>
+  <si>
+    <t>std.error</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Nmass | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t>15.336***</t>
+  </si>
+  <si>
+    <t>(0.480)</t>
+  </si>
+  <si>
+    <t>0.330</t>
+  </si>
+  <si>
+    <t>(0.579)</t>
+  </si>
+  <si>
+    <t>0.780</t>
+  </si>
+  <si>
+    <t>(0.592)</t>
+  </si>
+  <si>
+    <t>1.320*</t>
+  </si>
+  <si>
+    <t>(0.561)</t>
+  </si>
+  <si>
+    <t>0.562</t>
+  </si>
+  <si>
+    <t>1.160</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>0.133</t>
+  </si>
+  <si>
+    <t>0.298</t>
+  </si>
+  <si>
+    <t>124.0</t>
+  </si>
+  <si>
+    <t>Nmass | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t>17.393***</t>
+  </si>
+  <si>
+    <t>(1.314)</t>
+  </si>
+  <si>
+    <t>2.667</t>
+  </si>
+  <si>
+    <t>(2.629)</t>
+  </si>
+  <si>
+    <t>6.259*</t>
+  </si>
+  <si>
+    <t>(1.739)</t>
+  </si>
+  <si>
+    <t>2.227</t>
+  </si>
+  <si>
+    <t>0.000</t>
+  </si>
+  <si>
+    <t>2.277</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>0.558</t>
+  </si>
+  <si>
+    <t>51.7</t>
+  </si>
+  <si>
+    <t>Nmass | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t>11.606***</t>
+  </si>
+  <si>
+    <t>(0.448)</t>
+  </si>
+  <si>
+    <t>1.533*</t>
+  </si>
+  <si>
+    <t>(0.665)</t>
+  </si>
+  <si>
+    <t>0.429</t>
+  </si>
+  <si>
+    <t>(0.708)</t>
+  </si>
+  <si>
+    <t>-0.508</t>
+  </si>
+  <si>
+    <t>(0.601)</t>
+  </si>
+  <si>
+    <t>1.552</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>0.198</t>
+  </si>
+  <si>
+    <t>174.0</t>
+  </si>
+  <si>
+    <t>Nmass | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t>8.812***</t>
+  </si>
+  <si>
+    <t>(0.287)</t>
+  </si>
+  <si>
+    <t>1.192**</t>
+  </si>
+  <si>
+    <t>(0.386)</t>
+  </si>
+  <si>
+    <t>0.909*</t>
+  </si>
+  <si>
+    <t>(0.366)</t>
+  </si>
+  <si>
+    <t>-0.619</t>
+  </si>
+  <si>
+    <t>(0.369)</t>
+  </si>
+  <si>
+    <t>0.280</t>
+  </si>
+  <si>
+    <t>0.931</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>0.347</t>
+  </si>
+  <si>
+    <t>0.402</t>
+  </si>
+  <si>
+    <t>145.4</t>
+  </si>
+  <si>
+    <t>Nmass | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t>14.134***</t>
+  </si>
+  <si>
+    <t>(1.119)</t>
+  </si>
+  <si>
+    <t>3.403*</t>
+  </si>
+  <si>
+    <t>(1.180)</t>
+  </si>
+  <si>
+    <t>2.589+</t>
+  </si>
+  <si>
+    <t>(1.421)</t>
+  </si>
+  <si>
+    <t>1.359</t>
+  </si>
+  <si>
+    <t>(1.131)</t>
+  </si>
+  <si>
+    <t>1.417</t>
+  </si>
+  <si>
+    <t>1.920</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>0.234</t>
+  </si>
+  <si>
+    <t>0.504</t>
+  </si>
+  <si>
+    <t>92.6</t>
+  </si>
+  <si>
+    <t>Nmass | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t>10.434***</t>
+  </si>
+  <si>
+    <t>(0.699)</t>
+  </si>
+  <si>
+    <t>1.032</t>
+  </si>
+  <si>
+    <t>(0.989)</t>
+  </si>
+  <si>
+    <t>0.739</t>
+  </si>
+  <si>
+    <t>(1.308)</t>
+  </si>
+  <si>
+    <t>0.297</t>
+  </si>
+  <si>
+    <t>(0.947)</t>
+  </si>
+  <si>
+    <t>1.563</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>0.067</t>
+  </si>
+  <si>
+    <t>69.9</t>
+  </si>
+  <si>
+    <t>logNmass | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t>2.728***</t>
+  </si>
+  <si>
+    <t>(0.030)</t>
+  </si>
+  <si>
+    <t>0.021</t>
+  </si>
+  <si>
+    <t>(0.036)</t>
+  </si>
+  <si>
+    <t>0.049</t>
+  </si>
+  <si>
+    <t>0.082*</t>
+  </si>
+  <si>
+    <t>(0.034)</t>
+  </si>
+  <si>
+    <t>0.038</t>
+  </si>
+  <si>
+    <t>0.071</t>
+  </si>
+  <si>
+    <t>0.132</t>
+  </si>
+  <si>
+    <t>0.324</t>
+  </si>
+  <si>
+    <t>-54.8</t>
+  </si>
+  <si>
+    <t>logNmass | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t>2.849***</t>
+  </si>
+  <si>
+    <t>(0.070)</t>
+  </si>
+  <si>
+    <t>0.150</t>
+  </si>
+  <si>
+    <t>(0.141)</t>
+  </si>
+  <si>
+    <t>0.313*</t>
+  </si>
+  <si>
+    <t>(0.093)</t>
+  </si>
+  <si>
+    <t>0.120</t>
+  </si>
+  <si>
+    <t>0.122</t>
+  </si>
+  <si>
+    <t>0.520</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>logNmass | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t>2.442***</t>
+  </si>
+  <si>
+    <t>(0.039)</t>
+  </si>
+  <si>
+    <t>0.125*</t>
+  </si>
+  <si>
+    <t>(0.058)</t>
+  </si>
+  <si>
+    <t>(0.061)</t>
+  </si>
+  <si>
+    <t>-0.043</t>
+  </si>
+  <si>
+    <t>(0.052)</t>
+  </si>
+  <si>
+    <t>0.134</t>
+  </si>
+  <si>
+    <t>0.182</t>
+  </si>
+  <si>
+    <t>-26.6</t>
+  </si>
+  <si>
+    <t>logNmass | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t>2.168***</t>
+  </si>
+  <si>
+    <t>(0.032)</t>
+  </si>
+  <si>
+    <t>0.132**</t>
+  </si>
+  <si>
+    <t>(0.043)</t>
+  </si>
+  <si>
+    <t>0.102*</t>
+  </si>
+  <si>
+    <t>(0.041)</t>
+  </si>
+  <si>
+    <t>-0.071+</t>
+  </si>
+  <si>
+    <t>0.031</t>
+  </si>
+  <si>
+    <t>0.104</t>
+  </si>
+  <si>
+    <t>0.350</t>
+  </si>
+  <si>
+    <t>0.405</t>
+  </si>
+  <si>
+    <t>-52.1</t>
+  </si>
+  <si>
+    <t>logNmass | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t>2.648***</t>
+  </si>
+  <si>
+    <t>(0.065)</t>
+  </si>
+  <si>
+    <t>0.201**</t>
+  </si>
+  <si>
+    <t>0.163+</t>
+  </si>
+  <si>
+    <t>(0.078)</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>(0.062)</t>
+  </si>
+  <si>
+    <t>0.089</t>
+  </si>
+  <si>
+    <t>0.106</t>
+  </si>
+  <si>
+    <t>0.243</t>
+  </si>
+  <si>
+    <t>0.557</t>
+  </si>
+  <si>
+    <t>-5.4</t>
+  </si>
+  <si>
+    <t>logNmass | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t>2.338***</t>
+  </si>
+  <si>
+    <t>(0.064)</t>
+  </si>
+  <si>
+    <t>0.092</t>
+  </si>
+  <si>
+    <t>(0.091)</t>
+  </si>
+  <si>
+    <t>0.076</t>
+  </si>
+  <si>
+    <t>(0.121)</t>
+  </si>
+  <si>
+    <t>0.026</t>
+  </si>
+  <si>
+    <t>(0.087)</t>
+  </si>
+  <si>
+    <t>0.144</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>Narea | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t>1.920***</t>
+  </si>
+  <si>
+    <t>(0.075)</t>
+  </si>
+  <si>
+    <t>0.127</t>
+  </si>
+  <si>
+    <t>(0.108)</t>
+  </si>
+  <si>
+    <t>0.154</t>
+  </si>
+  <si>
+    <t>(0.120)</t>
+  </si>
+  <si>
+    <t>0.250*</t>
+  </si>
+  <si>
+    <t>(0.115)</t>
+  </si>
+  <si>
+    <t>0.248</t>
+  </si>
+  <si>
+    <t>0.123</t>
+  </si>
+  <si>
+    <t>22.3</t>
+  </si>
+  <si>
+    <t>Narea | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t>1.892***</t>
+  </si>
+  <si>
+    <t>(0.112)</t>
+  </si>
+  <si>
+    <t>-0.102</t>
+  </si>
+  <si>
+    <t>(0.224)</t>
+  </si>
+  <si>
+    <t>0.295+</t>
+  </si>
+  <si>
+    <t>(0.148)</t>
+  </si>
+  <si>
+    <t>0.159</t>
+  </si>
+  <si>
+    <t>0.194</t>
+  </si>
+  <si>
+    <t>0.342</t>
+  </si>
+  <si>
+    <t>12.3</t>
+  </si>
+  <si>
+    <t>Narea | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t>3.272***</t>
+  </si>
+  <si>
+    <t>(0.161)</t>
+  </si>
+  <si>
+    <t>0.320</t>
+  </si>
+  <si>
+    <t>(0.231)</t>
+  </si>
+  <si>
+    <t>(0.247)</t>
+  </si>
+  <si>
+    <t>-0.133</t>
+  </si>
+  <si>
+    <t>(0.209)</t>
+  </si>
+  <si>
+    <t>0.079</t>
+  </si>
+  <si>
+    <t>0.539</t>
+  </si>
+  <si>
+    <t>0.125</t>
+  </si>
+  <si>
+    <t>87.9</t>
+  </si>
+  <si>
+    <t>Narea | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t>2.882***</t>
+  </si>
+  <si>
+    <t>(0.260)</t>
+  </si>
+  <si>
+    <t>-0.057</t>
+  </si>
+  <si>
+    <t>(0.410)</t>
+  </si>
+  <si>
+    <t>-0.152</t>
+  </si>
+  <si>
+    <t>(0.380)</t>
+  </si>
+  <si>
+    <t>-0.486</t>
+  </si>
+  <si>
+    <t>(0.389)</t>
+  </si>
+  <si>
+    <t>0.046</t>
+  </si>
+  <si>
+    <t>1.003</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>0.037</t>
+  </si>
+  <si>
+    <t>153.0</t>
+  </si>
+  <si>
+    <t>Narea | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t>2.136***</t>
+  </si>
+  <si>
+    <t>(0.170)</t>
+  </si>
+  <si>
+    <t>0.702**</t>
+  </si>
+  <si>
+    <t>(0.222)</t>
+  </si>
+  <si>
+    <t>0.448</t>
+  </si>
+  <si>
+    <t>(0.268)</t>
+  </si>
+  <si>
+    <t>-0.022</t>
+  </si>
+  <si>
+    <t>(0.214)</t>
+  </si>
+  <si>
+    <t>0.094</t>
+  </si>
+  <si>
+    <t>0.365</t>
+  </si>
+  <si>
+    <t>0.433</t>
+  </si>
+  <si>
+    <t>0.468</t>
+  </si>
+  <si>
+    <t>33.2</t>
+  </si>
+  <si>
+    <t>Narea | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t>1.484***</t>
+  </si>
+  <si>
+    <t>(0.102)</t>
+  </si>
+  <si>
+    <t>(0.144)</t>
+  </si>
+  <si>
+    <t>0.069</t>
+  </si>
+  <si>
+    <t>(0.191)</t>
+  </si>
+  <si>
+    <t>-0.000</t>
+  </si>
+  <si>
+    <t>(0.138)</t>
+  </si>
+  <si>
+    <t>0.228</t>
+  </si>
+  <si>
+    <t>0.114</t>
+  </si>
+  <si>
+    <t>16.1</t>
+  </si>
+  <si>
+    <t>Cmass | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t>478.002***</t>
+  </si>
+  <si>
+    <t>(1.864)</t>
+  </si>
+  <si>
+    <t>2.498</t>
+  </si>
+  <si>
+    <t>(2.637)</t>
+  </si>
+  <si>
+    <t>-0.055</t>
+  </si>
+  <si>
+    <t>(2.819)</t>
+  </si>
+  <si>
+    <t>1.210</t>
+  </si>
+  <si>
+    <t>(2.718)</t>
+  </si>
+  <si>
+    <t>5.593</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>0.036</t>
+  </si>
+  <si>
+    <t>202.6</t>
+  </si>
+  <si>
+    <t>Cmass | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t>421.372***</t>
+  </si>
+  <si>
+    <t>(7.884)</t>
+  </si>
+  <si>
+    <t>25.773</t>
+  </si>
+  <si>
+    <t>(15.767)</t>
+  </si>
+  <si>
+    <t>9.125</t>
+  </si>
+  <si>
+    <t>(10.429)</t>
+  </si>
+  <si>
+    <t>16.973</t>
+  </si>
+  <si>
+    <t>13.655</t>
+  </si>
+  <si>
+    <t>0.265</t>
+  </si>
+  <si>
+    <t>80.4</t>
+  </si>
+  <si>
+    <t>Cmass | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t>489.936***</t>
+  </si>
+  <si>
+    <t>(2.460)</t>
+  </si>
+  <si>
+    <t>-2.251</t>
+  </si>
+  <si>
+    <t>(3.649)</t>
+  </si>
+  <si>
+    <t>0.623</t>
+  </si>
+  <si>
+    <t>(4.054)</t>
+  </si>
+  <si>
+    <t>-3.010</t>
+  </si>
+  <si>
+    <t>(3.353)</t>
+  </si>
+  <si>
+    <t>8.523</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>0.030</t>
+  </si>
+  <si>
+    <t>299.2</t>
+  </si>
+  <si>
+    <t>Cmass | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t>472.530***</t>
+  </si>
+  <si>
+    <t>(2.366)</t>
+  </si>
+  <si>
+    <t>-1.507</t>
+  </si>
+  <si>
+    <t>(3.312)</t>
+  </si>
+  <si>
+    <t>-7.836*</t>
+  </si>
+  <si>
+    <t>(3.124)</t>
+  </si>
+  <si>
+    <t>-2.897</t>
+  </si>
+  <si>
+    <t>(3.157)</t>
+  </si>
+  <si>
+    <t>2.177</t>
+  </si>
+  <si>
+    <t>8.111</t>
+  </si>
+  <si>
+    <t>0.118</t>
+  </si>
+  <si>
+    <t>0.177</t>
+  </si>
+  <si>
+    <t>347.0</t>
+  </si>
+  <si>
+    <t>Cmass | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t>438.175***</t>
+  </si>
+  <si>
+    <t>(3.416)</t>
+  </si>
+  <si>
+    <t>-3.352</t>
+  </si>
+  <si>
+    <t>(4.459)</t>
+  </si>
+  <si>
+    <t>4.616</t>
+  </si>
+  <si>
+    <t>(5.373)</t>
+  </si>
+  <si>
+    <t>-1.430</t>
+  </si>
+  <si>
+    <t>(4.301)</t>
+  </si>
+  <si>
+    <t>1.848</t>
+  </si>
+  <si>
+    <t>7.329</t>
+  </si>
+  <si>
+    <t>0.158</t>
+  </si>
+  <si>
+    <t>135.2</t>
+  </si>
+  <si>
+    <t>Cmass | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t>444.044***</t>
+  </si>
+  <si>
+    <t>(5.317)</t>
+  </si>
+  <si>
+    <t>0.897</t>
+  </si>
+  <si>
+    <t>(6.780)</t>
+  </si>
+  <si>
+    <t>17.429+</t>
+  </si>
+  <si>
+    <t>(9.040)</t>
+  </si>
+  <si>
+    <t>-2.611</t>
+  </si>
+  <si>
+    <t>(6.503)</t>
+  </si>
+  <si>
+    <t>4.022</t>
+  </si>
+  <si>
+    <t>10.639</t>
+  </si>
+  <si>
+    <t>0.220</t>
+  </si>
+  <si>
+    <t>0.318</t>
+  </si>
+  <si>
+    <t>124.8</t>
+  </si>
+  <si>
+    <t>Carea | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t>60.501***</t>
+  </si>
+  <si>
+    <t>(2.765)</t>
+  </si>
+  <si>
+    <t>2.382</t>
+  </si>
+  <si>
+    <t>(4.007)</t>
+  </si>
+  <si>
+    <t>0.288</t>
+  </si>
+  <si>
+    <t>(4.434)</t>
+  </si>
+  <si>
+    <t>2.011</t>
+  </si>
+  <si>
+    <t>(4.261)</t>
+  </si>
+  <si>
+    <t>9.170</t>
+  </si>
+  <si>
+    <t>0.014</t>
+  </si>
+  <si>
+    <t>253.4</t>
+  </si>
+  <si>
+    <t>Carea | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t>46.093***</t>
+  </si>
+  <si>
+    <t>(2.463)</t>
+  </si>
+  <si>
+    <t>-8.463*</t>
+  </si>
+  <si>
+    <t>(2.642)</t>
+  </si>
+  <si>
+    <t>-5.063*</t>
+  </si>
+  <si>
+    <t>(1.656)</t>
+  </si>
+  <si>
+    <t>-2.305</t>
+  </si>
+  <si>
+    <t>(1.759)</t>
+  </si>
+  <si>
+    <t>3.690</t>
+  </si>
+  <si>
+    <t>2.141</t>
+  </si>
+  <si>
+    <t>0.274</t>
+  </si>
+  <si>
+    <t>0.817</t>
+  </si>
+  <si>
+    <t>55.3</t>
+  </si>
+  <si>
+    <t>Carea | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t>139.527***</t>
+  </si>
+  <si>
+    <t>(5.780)</t>
+  </si>
+  <si>
+    <t>-6.085</t>
+  </si>
+  <si>
+    <t>(7.588)</t>
+  </si>
+  <si>
+    <t>2.265</t>
+  </si>
+  <si>
+    <t>(8.078)</t>
+  </si>
+  <si>
+    <t>-2.010</t>
+  </si>
+  <si>
+    <t>(6.856)</t>
+  </si>
+  <si>
+    <t>5.434</t>
+  </si>
+  <si>
+    <t>17.610</t>
+  </si>
+  <si>
+    <t>0.023</t>
+  </si>
+  <si>
+    <t>0.108</t>
+  </si>
+  <si>
+    <t>375.2</t>
+  </si>
+  <si>
+    <t>Carea | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t>131.985***</t>
+  </si>
+  <si>
+    <t>(3.549)</t>
+  </si>
+  <si>
+    <t>1.625</t>
+  </si>
+  <si>
+    <t>(5.612)</t>
+  </si>
+  <si>
+    <t>-1.843</t>
+  </si>
+  <si>
+    <t>(5.209)</t>
+  </si>
+  <si>
+    <t>6.197</t>
+  </si>
+  <si>
+    <t>(5.324)</t>
+  </si>
+  <si>
+    <t>13.747</t>
+  </si>
+  <si>
+    <t>393.7</t>
+  </si>
+  <si>
+    <t>Carea | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t>66.582***</t>
+  </si>
+  <si>
+    <t>(4.939)</t>
+  </si>
+  <si>
+    <t>5.565</t>
+  </si>
+  <si>
+    <t>(6.687)</t>
+  </si>
+  <si>
+    <t>0.796</t>
+  </si>
+  <si>
+    <t>(8.065)</t>
+  </si>
+  <si>
+    <t>-7.692</t>
+  </si>
+  <si>
+    <t>(6.467)</t>
+  </si>
+  <si>
+    <t>11.044</t>
+  </si>
+  <si>
+    <t>148.4</t>
+  </si>
+  <si>
+    <t>Carea | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t>63.680***</t>
+  </si>
+  <si>
+    <t>(2.815)</t>
+  </si>
+  <si>
+    <t>1.384</t>
+  </si>
+  <si>
+    <t>(3.981)</t>
+  </si>
+  <si>
+    <t>0.233</t>
+  </si>
+  <si>
+    <t>(5.266)</t>
+  </si>
+  <si>
+    <t>-2.826</t>
+  </si>
+  <si>
+    <t>(3.812)</t>
+  </si>
+  <si>
+    <t>6.295</t>
+  </si>
+  <si>
+    <t>0.072</t>
+  </si>
+  <si>
+    <t>108.9</t>
+  </si>
+  <si>
+    <t>logLCCC | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t>6.170***</t>
+  </si>
+  <si>
+    <t>(0.004)</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>(0.005)</t>
+  </si>
+  <si>
+    <t>(0.006)</t>
+  </si>
+  <si>
+    <t>0.003</t>
+  </si>
+  <si>
+    <t>0.012</t>
+  </si>
+  <si>
+    <t>-155.4</t>
+  </si>
+  <si>
+    <t>logLCCC |1000 | Clarisia</t>
+  </si>
+  <si>
+    <t>6.043***</t>
+  </si>
+  <si>
+    <t>(0.018)</t>
+  </si>
+  <si>
+    <t>0.060</t>
+  </si>
+  <si>
+    <t>(0.037)</t>
+  </si>
+  <si>
+    <t>(0.024)</t>
+  </si>
+  <si>
+    <t>0.040</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>0.263</t>
+  </si>
+  <si>
+    <t>-16.6</t>
+  </si>
+  <si>
+    <t>logLCCC  | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t>6.194***</t>
+  </si>
+  <si>
+    <t>-0.005</t>
+  </si>
+  <si>
+    <t>(0.008)</t>
+  </si>
+  <si>
+    <t>0.001</t>
+  </si>
+  <si>
+    <t>-0.006</t>
+  </si>
+  <si>
+    <t>(0.007)</t>
+  </si>
+  <si>
+    <t>0.018</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>-183.4</t>
+  </si>
+  <si>
+    <t>logLCCC  | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t>6.158***</t>
+  </si>
+  <si>
+    <t>-0.003</t>
+  </si>
+  <si>
+    <t>-0.017*</t>
+  </si>
+  <si>
+    <t>0.017</t>
+  </si>
+  <si>
+    <t>0.119</t>
+  </si>
+  <si>
+    <t>-219.7</t>
+  </si>
+  <si>
+    <t>logLCCC  | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t>6.083***</t>
+  </si>
+  <si>
+    <t>-0.008</t>
+  </si>
+  <si>
+    <t>(0.010)</t>
+  </si>
+  <si>
+    <t>0.010</t>
+  </si>
+  <si>
+    <t>(0.012)</t>
+  </si>
+  <si>
+    <t>0.004</t>
+  </si>
+  <si>
+    <t>-71.4</t>
+  </si>
+  <si>
+    <t>logLCCC  | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t>6.096***</t>
+  </si>
+  <si>
+    <t>0.002</t>
+  </si>
+  <si>
+    <t>(0.015)</t>
+  </si>
+  <si>
+    <t>0.039+</t>
+  </si>
+  <si>
+    <t>(0.021)</t>
+  </si>
+  <si>
+    <t>0.009</t>
+  </si>
+  <si>
+    <t>0.024</t>
+  </si>
+  <si>
+    <t>0.215</t>
+  </si>
+  <si>
+    <t>0.310</t>
+  </si>
+  <si>
+    <t>-45.7</t>
+  </si>
+  <si>
+    <t>LPC | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t>0.650***</t>
+  </si>
+  <si>
+    <t>(0.051)</t>
+  </si>
+  <si>
+    <t>-0.012</t>
+  </si>
+  <si>
+    <t>(0.066)</t>
+  </si>
+  <si>
+    <t>0.078</t>
+  </si>
+  <si>
+    <t>(0.068)</t>
+  </si>
+  <si>
+    <t>0.123+</t>
+  </si>
+  <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>0.136</t>
+  </si>
+  <si>
+    <t>0.131</t>
+  </si>
+  <si>
+    <t>0.238</t>
+  </si>
+  <si>
+    <t>-14.2</t>
+  </si>
+  <si>
+    <t>LPC | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t>0.793***</t>
+  </si>
+  <si>
+    <t>0.169</t>
+  </si>
+  <si>
+    <t>(0.155)</t>
+  </si>
+  <si>
+    <t>0.359*</t>
+  </si>
+  <si>
+    <t>(0.103)</t>
+  </si>
+  <si>
+    <t>0.381**</t>
+  </si>
+  <si>
+    <t>0.609</t>
+  </si>
+  <si>
+    <t>6.5</t>
+  </si>
+  <si>
+    <t>LPC | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t>0.784***</t>
+  </si>
+  <si>
+    <t>(0.079)</t>
+  </si>
+  <si>
+    <t>-0.015</t>
+  </si>
+  <si>
+    <t>(0.094)</t>
+  </si>
+  <si>
+    <t>0.526***</t>
+  </si>
+  <si>
+    <t>(0.100)</t>
+  </si>
+  <si>
+    <t>0.449***</t>
+  </si>
+  <si>
+    <t>0.093</t>
+  </si>
+  <si>
+    <t>0.218</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>0.518</t>
+  </si>
+  <si>
+    <t>0.593</t>
+  </si>
+  <si>
+    <t>16.4</t>
+  </si>
+  <si>
+    <t>LPC | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t>0.434***</t>
+  </si>
+  <si>
+    <t>(0.099)</t>
+  </si>
+  <si>
+    <t>(0.157)</t>
+  </si>
+  <si>
+    <t>0.444**</t>
+  </si>
+  <si>
+    <t>(0.146)</t>
+  </si>
+  <si>
+    <t>1.263***</t>
+  </si>
+  <si>
+    <t>(0.149)</t>
+  </si>
+  <si>
+    <t>0.384</t>
+  </si>
+  <si>
+    <t>0.643</t>
+  </si>
+  <si>
+    <t>64.6</t>
+  </si>
+  <si>
+    <t>LPC | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t>0.835***</t>
+  </si>
+  <si>
+    <t>-0.034</t>
+  </si>
+  <si>
+    <t>(0.151)</t>
+  </si>
+  <si>
+    <t>0.235</t>
+  </si>
+  <si>
+    <t>(0.182)</t>
+  </si>
+  <si>
+    <t>0.581**</t>
+  </si>
+  <si>
+    <t>0.250</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>0.542</t>
+  </si>
+  <si>
+    <t>19.3</t>
+  </si>
+  <si>
+    <t>LPC | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t>0.559***</t>
+  </si>
+  <si>
+    <t>(0.119)</t>
+  </si>
+  <si>
+    <t>(0.168)</t>
+  </si>
+  <si>
+    <t>0.161</t>
+  </si>
+  <si>
+    <t>(0.223)</t>
+  </si>
+  <si>
+    <t>1.077***</t>
+  </si>
+  <si>
+    <t>0.266</t>
+  </si>
+  <si>
+    <t>0.781</t>
+  </si>
+  <si>
+    <t>20.4</t>
+  </si>
+  <si>
+    <t>logLPC | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t>-0.446***</t>
+  </si>
+  <si>
+    <t>(0.076)</t>
+  </si>
+  <si>
+    <t>-0.038</t>
+  </si>
+  <si>
+    <t>0.121</t>
+  </si>
+  <si>
+    <t>(0.096)</t>
+  </si>
+  <si>
+    <t>0.178+</t>
+  </si>
+  <si>
+    <t>0.086</t>
+  </si>
+  <si>
+    <t>0.189</t>
+  </si>
+  <si>
+    <t>0.153</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>logLPC | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t>-0.233*</t>
+  </si>
+  <si>
+    <t>(0.067)</t>
+  </si>
+  <si>
+    <t>(0.134)</t>
+  </si>
+  <si>
+    <t>0.370**</t>
+  </si>
+  <si>
+    <t>(0.088)</t>
+  </si>
+  <si>
+    <t>0.386**</t>
+  </si>
+  <si>
+    <t>0.116</t>
+  </si>
+  <si>
+    <t>0.684</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>logLPC | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t>-0.257**</t>
+  </si>
+  <si>
+    <t>(0.081)</t>
+  </si>
+  <si>
+    <t>-0.019</t>
+  </si>
+  <si>
+    <t>(0.092)</t>
+  </si>
+  <si>
+    <t>0.489***</t>
+  </si>
+  <si>
+    <t>(0.098)</t>
+  </si>
+  <si>
+    <t>0.428***</t>
+  </si>
+  <si>
+    <t>(0.085)</t>
+  </si>
+  <si>
+    <t>0.213</t>
+  </si>
+  <si>
+    <t>0.491</t>
+  </si>
+  <si>
+    <t>0.592</t>
+  </si>
+  <si>
+    <t>14.9</t>
+  </si>
+  <si>
+    <t>logLPC | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t>-0.883***</t>
+  </si>
+  <si>
+    <t>(0.090)</t>
+  </si>
+  <si>
+    <t>0.027</t>
+  </si>
+  <si>
+    <t>(0.143)</t>
+  </si>
+  <si>
+    <t>0.687***</t>
+  </si>
+  <si>
+    <t>(0.132)</t>
+  </si>
+  <si>
+    <t>1.315***</t>
+  </si>
+  <si>
+    <t>(0.135)</t>
+  </si>
+  <si>
+    <t>0.349</t>
+  </si>
+  <si>
+    <t>0.707</t>
+  </si>
+  <si>
+    <t>55.8</t>
+  </si>
+  <si>
+    <t>logLPC | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t>-0.183*</t>
+  </si>
+  <si>
+    <t>(0.082)</t>
+  </si>
+  <si>
+    <t>-0.039</t>
+  </si>
+  <si>
+    <t>(0.111)</t>
+  </si>
+  <si>
+    <t>0.249+</t>
+  </si>
+  <si>
+    <t>0.492***</t>
+  </si>
+  <si>
+    <t>0.183</t>
+  </si>
+  <si>
+    <t>0.622</t>
+  </si>
+  <si>
+    <t>9.4</t>
+  </si>
+  <si>
+    <t>logLPC | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t>-0.585***</t>
+  </si>
+  <si>
+    <t>(0.086)</t>
+  </si>
+  <si>
+    <t>0.081</t>
+  </si>
+  <si>
+    <t>(0.122)</t>
+  </si>
+  <si>
+    <t>0.255</t>
+  </si>
+  <si>
+    <t>(0.162)</t>
+  </si>
+  <si>
+    <t>1.043***</t>
+  </si>
+  <si>
+    <t>(0.117)</t>
+  </si>
+  <si>
+    <t>0.193</t>
+  </si>
+  <si>
+    <t>0.858</t>
+  </si>
+  <si>
+    <t>11.4</t>
+  </si>
+  <si>
+    <t>Parea | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t>0.081***</t>
+  </si>
+  <si>
+    <t>0.011+</t>
+  </si>
+  <si>
+    <t>0.018**</t>
+  </si>
+  <si>
+    <t>0.279</t>
+  </si>
+  <si>
+    <t>0.380</t>
+  </si>
+  <si>
+    <t>-170.3</t>
+  </si>
+  <si>
+    <t>Parea | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t>0.087***</t>
+  </si>
+  <si>
+    <t>0.022+</t>
+  </si>
+  <si>
+    <t>(0.011)</t>
+  </si>
+  <si>
+    <t>0.033*</t>
+  </si>
+  <si>
+    <t>0.008</t>
+  </si>
+  <si>
+    <t>0.015</t>
+  </si>
+  <si>
+    <t>0.437</t>
+  </si>
+  <si>
+    <t>0.579</t>
+  </si>
+  <si>
+    <t>-27.6</t>
+  </si>
+  <si>
+    <t>Parea | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t>0.221***</t>
+  </si>
+  <si>
+    <t>0.167**</t>
+  </si>
+  <si>
+    <t>(0.056)</t>
+  </si>
+  <si>
+    <t>0.174***</t>
+  </si>
+  <si>
+    <t>(0.047)</t>
+  </si>
+  <si>
+    <t>0.011</t>
+  </si>
+  <si>
+    <t>0.345</t>
+  </si>
+  <si>
+    <t>0.351</t>
+  </si>
+  <si>
+    <t>-34.5</t>
+  </si>
+  <si>
+    <t>Parea | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t>0.122***</t>
+  </si>
+  <si>
+    <t>(0.033)</t>
+  </si>
+  <si>
+    <t>-0.001</t>
+  </si>
+  <si>
+    <t>0.122*</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>0.382***</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>0.126</t>
+  </si>
+  <si>
+    <t>0.604</t>
+  </si>
+  <si>
+    <t>-38.1</t>
+  </si>
+  <si>
+    <t>Parea | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t>0.125***</t>
+  </si>
+  <si>
+    <t>(0.027)</t>
+  </si>
+  <si>
+    <t>(0.044)</t>
+  </si>
+  <si>
+    <t>0.093*</t>
+  </si>
+  <si>
+    <t>(0.035)</t>
+  </si>
+  <si>
+    <t>0.319</t>
+  </si>
+  <si>
+    <t>-29.1</t>
+  </si>
+  <si>
+    <t>Parea | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t>0.080***</t>
+  </si>
+  <si>
+    <t>(0.016)</t>
+  </si>
+  <si>
+    <t>(0.023)</t>
+  </si>
+  <si>
+    <t>0.020</t>
+  </si>
+  <si>
+    <t>0.145***</t>
+  </si>
+  <si>
+    <t>(0.022)</t>
+  </si>
+  <si>
+    <t>0.778</t>
+  </si>
+  <si>
+    <t>-35.7</t>
+  </si>
+  <si>
+    <t>Leaf N:P | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t>24.474***</t>
+  </si>
+  <si>
+    <t>(1.600)</t>
+  </si>
+  <si>
+    <t>1.444</t>
+  </si>
+  <si>
+    <t>(2.188)</t>
+  </si>
+  <si>
+    <t>-1.987</t>
+  </si>
+  <si>
+    <t>(2.331)</t>
+  </si>
+  <si>
+    <t>-2.163</t>
+  </si>
+  <si>
+    <t>(2.223)</t>
+  </si>
+  <si>
+    <t>1.168</t>
+  </si>
+  <si>
+    <t>4.690</t>
+  </si>
+  <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>0.140</t>
+  </si>
+  <si>
+    <t>211.6</t>
+  </si>
+  <si>
+    <t>Leaf N:P | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t>21.867***</t>
+  </si>
+  <si>
+    <t>(1.675)</t>
+  </si>
+  <si>
+    <t>-0.995</t>
+  </si>
+  <si>
+    <t>(3.323)</t>
+  </si>
+  <si>
+    <t>-1.076</t>
+  </si>
+  <si>
+    <t>(2.186)</t>
+  </si>
+  <si>
+    <t>-4.953+</t>
+  </si>
+  <si>
+    <t>(2.198)</t>
+  </si>
+  <si>
+    <t>0.488</t>
+  </si>
+  <si>
+    <t>2.859</t>
+  </si>
+  <si>
+    <t>0.356</t>
+  </si>
+  <si>
+    <t>0.374</t>
+  </si>
+  <si>
+    <t>55.5</t>
+  </si>
+  <si>
+    <t>Leaf N:P | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t>15.015***</t>
+  </si>
+  <si>
+    <t>(0.948)</t>
+  </si>
+  <si>
+    <t>2.175*</t>
+  </si>
+  <si>
+    <t>(0.897)</t>
+  </si>
+  <si>
+    <t>-5.308***</t>
+  </si>
+  <si>
+    <t>(0.953)</t>
+  </si>
+  <si>
+    <t>-5.939***</t>
+  </si>
+  <si>
+    <t>(0.810)</t>
+  </si>
+  <si>
+    <t>1.467</t>
+  </si>
+  <si>
+    <t>2.071</t>
+  </si>
+  <si>
+    <t>0.653</t>
+  </si>
+  <si>
+    <t>0.769</t>
+  </si>
+  <si>
+    <t>203.1</t>
+  </si>
+  <si>
+    <t>Leaf N:P | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t>23.224***</t>
+  </si>
+  <si>
+    <t>(1.132)</t>
+  </si>
+  <si>
+    <t>0.308</t>
+  </si>
+  <si>
+    <t>(1.582)</t>
+  </si>
+  <si>
+    <t>-11.021***</t>
+  </si>
+  <si>
+    <t>(1.492)</t>
+  </si>
+  <si>
+    <t>-16.982***</t>
+  </si>
+  <si>
+    <t>(1.508)</t>
+  </si>
+  <si>
+    <t>1.048</t>
+  </si>
+  <si>
+    <t>3.874</t>
+  </si>
+  <si>
+    <t>0.772</t>
+  </si>
+  <si>
+    <t>0.788</t>
+  </si>
+  <si>
+    <t>279.1</t>
+  </si>
+  <si>
+    <t>Leaf N:P | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t>17.046***</t>
+  </si>
+  <si>
+    <t>(1.615)</t>
+  </si>
+  <si>
+    <t>4.648*</t>
+  </si>
+  <si>
+    <t>(2.036)</t>
+  </si>
+  <si>
+    <t>-1.420</t>
+  </si>
+  <si>
+    <t>(2.453)</t>
+  </si>
+  <si>
+    <t>-6.056**</t>
+  </si>
+  <si>
+    <t>(1.961)</t>
+  </si>
+  <si>
+    <t>1.197</t>
+  </si>
+  <si>
+    <t>3.337</t>
+  </si>
+  <si>
+    <t>0.599</t>
+  </si>
+  <si>
+    <t>0.645</t>
+  </si>
+  <si>
+    <t>109.1</t>
+  </si>
+  <si>
+    <t>Leaf N:P | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t>18.652***</t>
+  </si>
+  <si>
+    <t>(1.117)</t>
+  </si>
+  <si>
+    <t>(1.580)</t>
+  </si>
+  <si>
+    <t>-3.078</t>
+  </si>
+  <si>
+    <t>(2.090)</t>
+  </si>
+  <si>
+    <t>-11.345***</t>
+  </si>
+  <si>
+    <t>(1.513)</t>
+  </si>
+  <si>
+    <t>0.823</t>
+  </si>
+  <si>
+    <t>83.1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2272,11 +2278,20 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:O63" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:O63" totalsRowShown="0">
   <autoFilter ref="A1:O63"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Modelo"/>
@@ -2577,11 +2592,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O63"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2628,7 +2646,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -2675,7 +2693,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -2722,7 +2740,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -2769,7 +2787,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -2816,7 +2834,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>58</v>
       </c>
@@ -2863,7 +2881,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>71</v>
       </c>
@@ -2910,7 +2928,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>86</v>
       </c>
@@ -2957,7 +2975,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>101</v>
       </c>
@@ -3004,7 +3022,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>114</v>
       </c>
@@ -3051,7 +3069,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>127</v>
       </c>
@@ -3098,7 +3116,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>138</v>
       </c>
@@ -3145,7 +3163,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>149</v>
       </c>
@@ -3192,7 +3210,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>162</v>
       </c>
@@ -3239,7 +3257,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>175</v>
       </c>
@@ -3286,7 +3304,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>186</v>
       </c>
@@ -3333,7 +3351,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>198</v>
       </c>
@@ -3380,7 +3398,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>209</v>
       </c>
@@ -3427,7 +3445,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>221</v>
       </c>
@@ -3474,7 +3492,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>236</v>
       </c>
@@ -3521,7 +3539,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>250</v>
       </c>
@@ -3568,7 +3586,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>261</v>
       </c>
@@ -3615,7 +3633,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>274</v>
       </c>
@@ -3662,7 +3680,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>285</v>
       </c>
@@ -3709,7 +3727,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>298</v>
       </c>
@@ -3756,7 +3774,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>312</v>
       </c>
@@ -3803,7 +3821,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>325</v>
       </c>
@@ -3850,7 +3868,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>339</v>
       </c>
@@ -3897,7 +3915,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>351</v>
       </c>
@@ -3944,7 +3962,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>365</v>
       </c>
@@ -3991,7 +4009,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>379</v>
       </c>
@@ -4038,7 +4056,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>390</v>
       </c>
@@ -4085,7 +4103,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>401</v>
       </c>
@@ -4132,7 +4150,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>413</v>
       </c>
@@ -4179,7 +4197,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>422</v>
       </c>
@@ -4226,7 +4244,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>432</v>
       </c>
@@ -4273,7 +4291,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>442</v>
       </c>
@@ -4320,7 +4338,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>449</v>
       </c>
@@ -4367,7 +4385,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>457</v>
       </c>
@@ -4414,7 +4432,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>468</v>
       </c>
@@ -4461,7 +4479,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>481</v>
       </c>
@@ -4508,7 +4526,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>490</v>
       </c>
@@ -4555,7 +4573,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>504</v>
       </c>
@@ -4602,7 +4620,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>515</v>
       </c>
@@ -4649,7 +4667,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>526</v>
       </c>
@@ -4696,7 +4714,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>536</v>
       </c>
@@ -4743,7 +4761,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>547</v>
       </c>
@@ -4790,7 +4808,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>557</v>
       </c>
@@ -4837,7 +4855,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>570</v>
       </c>
@@ -4884,7 +4902,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>582</v>
       </c>
@@ -4931,7 +4949,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>592</v>
       </c>
@@ -4978,7 +4996,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>604</v>
       </c>
@@ -5025,7 +5043,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>611</v>
       </c>
@@ -5072,7 +5090,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>621</v>
       </c>
@@ -5119,7 +5137,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>631</v>
       </c>
@@ -5166,7 +5184,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>642</v>
       </c>
@@ -5213,7 +5231,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>650</v>
       </c>
@@ -5260,7 +5278,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>659</v>
       </c>
@@ -5307,7 +5325,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>673</v>
       </c>
@@ -5354,7 +5372,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>687</v>
       </c>
@@ -5401,7 +5419,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>701</v>
       </c>
@@ -5448,7 +5466,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>715</v>
       </c>
@@ -5495,7 +5513,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>729</v>
       </c>
@@ -5544,9 +5562,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/NUMEX_pre_RStudio/models_est.xlsx
+++ b/NUMEX_pre_RStudio/models_est.xlsx
@@ -1,2248 +1,2242 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\selene.baez\Downloads\NUMEX_preliminar\NUMEX_pre_RStudio\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="739">
-  <si>
-    <t>Modelo</t>
-  </si>
-  <si>
-    <t>estimates</t>
-  </si>
-  <si>
-    <t>estimates.1</t>
-  </si>
-  <si>
-    <t>estimates.2</t>
-  </si>
-  <si>
-    <t>estimates.3</t>
-  </si>
-  <si>
-    <t>estimates.4</t>
-  </si>
-  <si>
-    <t>estimates.5</t>
-  </si>
-  <si>
-    <t>estimates.6</t>
-  </si>
-  <si>
-    <t>estimates.7</t>
-  </si>
-  <si>
-    <t>estimates.8</t>
-  </si>
-  <si>
-    <t>estimates.9</t>
-  </si>
-  <si>
-    <t>gof</t>
-  </si>
-  <si>
-    <t>gof.1</t>
-  </si>
-  <si>
-    <t>gof.2</t>
-  </si>
-  <si>
-    <t>gof.3</t>
-  </si>
-  <si>
-    <t>term</t>
-  </si>
-  <si>
-    <t>(Intercept)</t>
-  </si>
-  <si>
-    <t>SUBN</t>
-  </si>
-  <si>
-    <t>SUBNP</t>
-  </si>
-  <si>
-    <t>SUBP</t>
-  </si>
-  <si>
-    <t>SD (Intercept Bloque)</t>
-  </si>
-  <si>
-    <t>SD (Observations)</t>
-  </si>
-  <si>
-    <t>Num.Obs.</t>
-  </si>
-  <si>
-    <t>R2 Marg.</t>
-  </si>
-  <si>
-    <t>R2 Cond.</t>
-  </si>
-  <si>
-    <t>AIC</t>
-  </si>
-  <si>
-    <t>statistic</t>
-  </si>
-  <si>
-    <t>estimate</t>
-  </si>
-  <si>
-    <t>std.error</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Nmass | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t>15.336***</t>
-  </si>
-  <si>
-    <t>(0.480)</t>
-  </si>
-  <si>
-    <t>0.330</t>
-  </si>
-  <si>
-    <t>(0.579)</t>
-  </si>
-  <si>
-    <t>0.780</t>
-  </si>
-  <si>
-    <t>(0.592)</t>
-  </si>
-  <si>
-    <t>1.320*</t>
-  </si>
-  <si>
-    <t>(0.561)</t>
-  </si>
-  <si>
-    <t>0.562</t>
-  </si>
-  <si>
-    <t>1.160</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>0.133</t>
-  </si>
-  <si>
-    <t>0.298</t>
-  </si>
-  <si>
-    <t>124.0</t>
-  </si>
-  <si>
-    <t>Nmass | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t>17.393***</t>
-  </si>
-  <si>
-    <t>(1.314)</t>
-  </si>
-  <si>
-    <t>2.667</t>
-  </si>
-  <si>
-    <t>(2.629)</t>
-  </si>
-  <si>
-    <t>6.259*</t>
-  </si>
-  <si>
-    <t>(1.739)</t>
-  </si>
-  <si>
-    <t>2.227</t>
-  </si>
-  <si>
-    <t>0.000</t>
-  </si>
-  <si>
-    <t>2.277</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>0.558</t>
-  </si>
-  <si>
-    <t>51.7</t>
-  </si>
-  <si>
-    <t>Nmass | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t>11.606***</t>
-  </si>
-  <si>
-    <t>(0.448)</t>
-  </si>
-  <si>
-    <t>1.533*</t>
-  </si>
-  <si>
-    <t>(0.665)</t>
-  </si>
-  <si>
-    <t>0.429</t>
-  </si>
-  <si>
-    <t>(0.708)</t>
-  </si>
-  <si>
-    <t>-0.508</t>
-  </si>
-  <si>
-    <t>(0.601)</t>
-  </si>
-  <si>
-    <t>1.552</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>0.198</t>
-  </si>
-  <si>
-    <t>174.0</t>
-  </si>
-  <si>
-    <t>Nmass | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t>8.812***</t>
-  </si>
-  <si>
-    <t>(0.287)</t>
-  </si>
-  <si>
-    <t>1.192**</t>
-  </si>
-  <si>
-    <t>(0.386)</t>
-  </si>
-  <si>
-    <t>0.909*</t>
-  </si>
-  <si>
-    <t>(0.366)</t>
-  </si>
-  <si>
-    <t>-0.619</t>
-  </si>
-  <si>
-    <t>(0.369)</t>
-  </si>
-  <si>
-    <t>0.280</t>
-  </si>
-  <si>
-    <t>0.931</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>0.347</t>
-  </si>
-  <si>
-    <t>0.402</t>
-  </si>
-  <si>
-    <t>145.4</t>
-  </si>
-  <si>
-    <t>Nmass | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t>14.134***</t>
-  </si>
-  <si>
-    <t>(1.119)</t>
-  </si>
-  <si>
-    <t>3.403*</t>
-  </si>
-  <si>
-    <t>(1.180)</t>
-  </si>
-  <si>
-    <t>2.589+</t>
-  </si>
-  <si>
-    <t>(1.421)</t>
-  </si>
-  <si>
-    <t>1.359</t>
-  </si>
-  <si>
-    <t>(1.131)</t>
-  </si>
-  <si>
-    <t>1.417</t>
-  </si>
-  <si>
-    <t>1.920</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>0.234</t>
-  </si>
-  <si>
-    <t>0.504</t>
-  </si>
-  <si>
-    <t>92.6</t>
-  </si>
-  <si>
-    <t>Nmass | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t>10.434***</t>
-  </si>
-  <si>
-    <t>(0.699)</t>
-  </si>
-  <si>
-    <t>1.032</t>
-  </si>
-  <si>
-    <t>(0.989)</t>
-  </si>
-  <si>
-    <t>0.739</t>
-  </si>
-  <si>
-    <t>(1.308)</t>
-  </si>
-  <si>
-    <t>0.297</t>
-  </si>
-  <si>
-    <t>(0.947)</t>
-  </si>
-  <si>
-    <t>1.563</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>0.067</t>
-  </si>
-  <si>
-    <t>69.9</t>
-  </si>
-  <si>
-    <t>logNmass | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t>2.728***</t>
-  </si>
-  <si>
-    <t>(0.030)</t>
-  </si>
-  <si>
-    <t>0.021</t>
-  </si>
-  <si>
-    <t>(0.036)</t>
-  </si>
-  <si>
-    <t>0.049</t>
-  </si>
-  <si>
-    <t>0.082*</t>
-  </si>
-  <si>
-    <t>(0.034)</t>
-  </si>
-  <si>
-    <t>0.038</t>
-  </si>
-  <si>
-    <t>0.071</t>
-  </si>
-  <si>
-    <t>0.132</t>
-  </si>
-  <si>
-    <t>0.324</t>
-  </si>
-  <si>
-    <t>-54.8</t>
-  </si>
-  <si>
-    <t>logNmass | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t>2.849***</t>
-  </si>
-  <si>
-    <t>(0.070)</t>
-  </si>
-  <si>
-    <t>0.150</t>
-  </si>
-  <si>
-    <t>(0.141)</t>
-  </si>
-  <si>
-    <t>0.313*</t>
-  </si>
-  <si>
-    <t>(0.093)</t>
-  </si>
-  <si>
-    <t>0.120</t>
-  </si>
-  <si>
-    <t>0.122</t>
-  </si>
-  <si>
-    <t>0.520</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>logNmass | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t>2.442***</t>
-  </si>
-  <si>
-    <t>(0.039)</t>
-  </si>
-  <si>
-    <t>0.125*</t>
-  </si>
-  <si>
-    <t>(0.058)</t>
-  </si>
-  <si>
-    <t>(0.061)</t>
-  </si>
-  <si>
-    <t>-0.043</t>
-  </si>
-  <si>
-    <t>(0.052)</t>
-  </si>
-  <si>
-    <t>0.134</t>
-  </si>
-  <si>
-    <t>0.182</t>
-  </si>
-  <si>
-    <t>-26.6</t>
-  </si>
-  <si>
-    <t>logNmass | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t>2.168***</t>
-  </si>
-  <si>
-    <t>(0.032)</t>
-  </si>
-  <si>
-    <t>0.132**</t>
-  </si>
-  <si>
-    <t>(0.043)</t>
-  </si>
-  <si>
-    <t>0.102*</t>
-  </si>
-  <si>
-    <t>(0.041)</t>
-  </si>
-  <si>
-    <t>-0.071+</t>
-  </si>
-  <si>
-    <t>0.031</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>0.350</t>
-  </si>
-  <si>
-    <t>0.405</t>
-  </si>
-  <si>
-    <t>-52.1</t>
-  </si>
-  <si>
-    <t>logNmass | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t>2.648***</t>
-  </si>
-  <si>
-    <t>(0.065)</t>
-  </si>
-  <si>
-    <t>0.201**</t>
-  </si>
-  <si>
-    <t>0.163+</t>
-  </si>
-  <si>
-    <t>(0.078)</t>
-  </si>
-  <si>
-    <t>0.088</t>
-  </si>
-  <si>
-    <t>(0.062)</t>
-  </si>
-  <si>
-    <t>0.089</t>
-  </si>
-  <si>
-    <t>0.106</t>
-  </si>
-  <si>
-    <t>0.243</t>
-  </si>
-  <si>
-    <t>0.557</t>
-  </si>
-  <si>
-    <t>-5.4</t>
-  </si>
-  <si>
-    <t>logNmass | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t>2.338***</t>
-  </si>
-  <si>
-    <t>(0.064)</t>
-  </si>
-  <si>
-    <t>0.092</t>
-  </si>
-  <si>
-    <t>(0.091)</t>
-  </si>
-  <si>
-    <t>0.076</t>
-  </si>
-  <si>
-    <t>(0.121)</t>
-  </si>
-  <si>
-    <t>0.026</t>
-  </si>
-  <si>
-    <t>(0.087)</t>
-  </si>
-  <si>
-    <t>0.144</t>
-  </si>
-  <si>
-    <t>3.2</t>
-  </si>
-  <si>
-    <t>Narea | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t>1.920***</t>
-  </si>
-  <si>
-    <t>(0.075)</t>
-  </si>
-  <si>
-    <t>0.127</t>
-  </si>
-  <si>
-    <t>(0.108)</t>
-  </si>
-  <si>
-    <t>0.154</t>
-  </si>
-  <si>
-    <t>(0.120)</t>
-  </si>
-  <si>
-    <t>0.250*</t>
-  </si>
-  <si>
-    <t>(0.115)</t>
-  </si>
-  <si>
-    <t>0.248</t>
-  </si>
-  <si>
-    <t>0.123</t>
-  </si>
-  <si>
-    <t>22.3</t>
-  </si>
-  <si>
-    <t>Narea | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t>1.892***</t>
-  </si>
-  <si>
-    <t>(0.112)</t>
-  </si>
-  <si>
-    <t>-0.102</t>
-  </si>
-  <si>
-    <t>(0.224)</t>
-  </si>
-  <si>
-    <t>0.295+</t>
-  </si>
-  <si>
-    <t>(0.148)</t>
-  </si>
-  <si>
-    <t>0.159</t>
-  </si>
-  <si>
-    <t>0.194</t>
-  </si>
-  <si>
-    <t>0.342</t>
-  </si>
-  <si>
-    <t>12.3</t>
-  </si>
-  <si>
-    <t>Narea | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t>3.272***</t>
-  </si>
-  <si>
-    <t>(0.161)</t>
-  </si>
-  <si>
-    <t>0.320</t>
-  </si>
-  <si>
-    <t>(0.231)</t>
-  </si>
-  <si>
-    <t>(0.247)</t>
-  </si>
-  <si>
-    <t>-0.133</t>
-  </si>
-  <si>
-    <t>(0.209)</t>
-  </si>
-  <si>
-    <t>0.079</t>
-  </si>
-  <si>
-    <t>0.539</t>
-  </si>
-  <si>
-    <t>0.125</t>
-  </si>
-  <si>
-    <t>87.9</t>
-  </si>
-  <si>
-    <t>Narea | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t>2.882***</t>
-  </si>
-  <si>
-    <t>(0.260)</t>
-  </si>
-  <si>
-    <t>-0.057</t>
-  </si>
-  <si>
-    <t>(0.410)</t>
-  </si>
-  <si>
-    <t>-0.152</t>
-  </si>
-  <si>
-    <t>(0.380)</t>
-  </si>
-  <si>
-    <t>-0.486</t>
-  </si>
-  <si>
-    <t>(0.389)</t>
-  </si>
-  <si>
-    <t>0.046</t>
-  </si>
-  <si>
-    <t>1.003</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>0.035</t>
-  </si>
-  <si>
-    <t>0.037</t>
-  </si>
-  <si>
-    <t>153.0</t>
-  </si>
-  <si>
-    <t>Narea | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t>2.136***</t>
-  </si>
-  <si>
-    <t>(0.170)</t>
-  </si>
-  <si>
-    <t>0.702**</t>
-  </si>
-  <si>
-    <t>(0.222)</t>
-  </si>
-  <si>
-    <t>0.448</t>
-  </si>
-  <si>
-    <t>(0.268)</t>
-  </si>
-  <si>
-    <t>-0.022</t>
-  </si>
-  <si>
-    <t>(0.214)</t>
-  </si>
-  <si>
-    <t>0.094</t>
-  </si>
-  <si>
-    <t>0.365</t>
-  </si>
-  <si>
-    <t>0.433</t>
-  </si>
-  <si>
-    <t>0.468</t>
-  </si>
-  <si>
-    <t>33.2</t>
-  </si>
-  <si>
-    <t>Narea | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t>1.484***</t>
-  </si>
-  <si>
-    <t>(0.102)</t>
-  </si>
-  <si>
-    <t>(0.144)</t>
-  </si>
-  <si>
-    <t>0.069</t>
-  </si>
-  <si>
-    <t>(0.191)</t>
-  </si>
-  <si>
-    <t>-0.000</t>
-  </si>
-  <si>
-    <t>(0.138)</t>
-  </si>
-  <si>
-    <t>0.228</t>
-  </si>
-  <si>
-    <t>0.114</t>
-  </si>
-  <si>
-    <t>16.1</t>
-  </si>
-  <si>
-    <t>Cmass | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t>478.002***</t>
-  </si>
-  <si>
-    <t>(1.864)</t>
-  </si>
-  <si>
-    <t>2.498</t>
-  </si>
-  <si>
-    <t>(2.637)</t>
-  </si>
-  <si>
-    <t>-0.055</t>
-  </si>
-  <si>
-    <t>(2.819)</t>
-  </si>
-  <si>
-    <t>1.210</t>
-  </si>
-  <si>
-    <t>(2.718)</t>
-  </si>
-  <si>
-    <t>5.593</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>0.036</t>
-  </si>
-  <si>
-    <t>202.6</t>
-  </si>
-  <si>
-    <t>Cmass | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t>421.372***</t>
-  </si>
-  <si>
-    <t>(7.884)</t>
-  </si>
-  <si>
-    <t>25.773</t>
-  </si>
-  <si>
-    <t>(15.767)</t>
-  </si>
-  <si>
-    <t>9.125</t>
-  </si>
-  <si>
-    <t>(10.429)</t>
-  </si>
-  <si>
-    <t>16.973</t>
-  </si>
-  <si>
-    <t>13.655</t>
-  </si>
-  <si>
-    <t>0.265</t>
-  </si>
-  <si>
-    <t>80.4</t>
-  </si>
-  <si>
-    <t>Cmass | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t>489.936***</t>
-  </si>
-  <si>
-    <t>(2.460)</t>
-  </si>
-  <si>
-    <t>-2.251</t>
-  </si>
-  <si>
-    <t>(3.649)</t>
-  </si>
-  <si>
-    <t>0.623</t>
-  </si>
-  <si>
-    <t>(4.054)</t>
-  </si>
-  <si>
-    <t>-3.010</t>
-  </si>
-  <si>
-    <t>(3.353)</t>
-  </si>
-  <si>
-    <t>8.523</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>0.030</t>
-  </si>
-  <si>
-    <t>299.2</t>
-  </si>
-  <si>
-    <t>Cmass | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t>472.530***</t>
-  </si>
-  <si>
-    <t>(2.366)</t>
-  </si>
-  <si>
-    <t>-1.507</t>
-  </si>
-  <si>
-    <t>(3.312)</t>
-  </si>
-  <si>
-    <t>-7.836*</t>
-  </si>
-  <si>
-    <t>(3.124)</t>
-  </si>
-  <si>
-    <t>-2.897</t>
-  </si>
-  <si>
-    <t>(3.157)</t>
-  </si>
-  <si>
-    <t>2.177</t>
-  </si>
-  <si>
-    <t>8.111</t>
-  </si>
-  <si>
-    <t>0.118</t>
-  </si>
-  <si>
-    <t>0.177</t>
-  </si>
-  <si>
-    <t>347.0</t>
-  </si>
-  <si>
-    <t>Cmass | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t>438.175***</t>
-  </si>
-  <si>
-    <t>(3.416)</t>
-  </si>
-  <si>
-    <t>-3.352</t>
-  </si>
-  <si>
-    <t>(4.459)</t>
-  </si>
-  <si>
-    <t>4.616</t>
-  </si>
-  <si>
-    <t>(5.373)</t>
-  </si>
-  <si>
-    <t>-1.430</t>
-  </si>
-  <si>
-    <t>(4.301)</t>
-  </si>
-  <si>
-    <t>1.848</t>
-  </si>
-  <si>
-    <t>7.329</t>
-  </si>
-  <si>
-    <t>0.158</t>
-  </si>
-  <si>
-    <t>135.2</t>
-  </si>
-  <si>
-    <t>Cmass | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t>444.044***</t>
-  </si>
-  <si>
-    <t>(5.317)</t>
-  </si>
-  <si>
-    <t>0.897</t>
-  </si>
-  <si>
-    <t>(6.780)</t>
-  </si>
-  <si>
-    <t>17.429+</t>
-  </si>
-  <si>
-    <t>(9.040)</t>
-  </si>
-  <si>
-    <t>-2.611</t>
-  </si>
-  <si>
-    <t>(6.503)</t>
-  </si>
-  <si>
-    <t>4.022</t>
-  </si>
-  <si>
-    <t>10.639</t>
-  </si>
-  <si>
-    <t>0.220</t>
-  </si>
-  <si>
-    <t>0.318</t>
-  </si>
-  <si>
-    <t>124.8</t>
-  </si>
-  <si>
-    <t>Carea | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t>60.501***</t>
-  </si>
-  <si>
-    <t>(2.765)</t>
-  </si>
-  <si>
-    <t>2.382</t>
-  </si>
-  <si>
-    <t>(4.007)</t>
-  </si>
-  <si>
-    <t>0.288</t>
-  </si>
-  <si>
-    <t>(4.434)</t>
-  </si>
-  <si>
-    <t>2.011</t>
-  </si>
-  <si>
-    <t>(4.261)</t>
-  </si>
-  <si>
-    <t>9.170</t>
-  </si>
-  <si>
-    <t>0.014</t>
-  </si>
-  <si>
-    <t>253.4</t>
-  </si>
-  <si>
-    <t>Carea | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t>46.093***</t>
-  </si>
-  <si>
-    <t>(2.463)</t>
-  </si>
-  <si>
-    <t>-8.463*</t>
-  </si>
-  <si>
-    <t>(2.642)</t>
-  </si>
-  <si>
-    <t>-5.063*</t>
-  </si>
-  <si>
-    <t>(1.656)</t>
-  </si>
-  <si>
-    <t>-2.305</t>
-  </si>
-  <si>
-    <t>(1.759)</t>
-  </si>
-  <si>
-    <t>3.690</t>
-  </si>
-  <si>
-    <t>2.141</t>
-  </si>
-  <si>
-    <t>0.274</t>
-  </si>
-  <si>
-    <t>0.817</t>
-  </si>
-  <si>
-    <t>55.3</t>
-  </si>
-  <si>
-    <t>Carea | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t>139.527***</t>
-  </si>
-  <si>
-    <t>(5.780)</t>
-  </si>
-  <si>
-    <t>-6.085</t>
-  </si>
-  <si>
-    <t>(7.588)</t>
-  </si>
-  <si>
-    <t>2.265</t>
-  </si>
-  <si>
-    <t>(8.078)</t>
-  </si>
-  <si>
-    <t>-2.010</t>
-  </si>
-  <si>
-    <t>(6.856)</t>
-  </si>
-  <si>
-    <t>5.434</t>
-  </si>
-  <si>
-    <t>17.610</t>
-  </si>
-  <si>
-    <t>0.023</t>
-  </si>
-  <si>
-    <t>0.108</t>
-  </si>
-  <si>
-    <t>375.2</t>
-  </si>
-  <si>
-    <t>Carea | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t>131.985***</t>
-  </si>
-  <si>
-    <t>(3.549)</t>
-  </si>
-  <si>
-    <t>1.625</t>
-  </si>
-  <si>
-    <t>(5.612)</t>
-  </si>
-  <si>
-    <t>-1.843</t>
-  </si>
-  <si>
-    <t>(5.209)</t>
-  </si>
-  <si>
-    <t>6.197</t>
-  </si>
-  <si>
-    <t>(5.324)</t>
-  </si>
-  <si>
-    <t>13.747</t>
-  </si>
-  <si>
-    <t>393.7</t>
-  </si>
-  <si>
-    <t>Carea | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t>66.582***</t>
-  </si>
-  <si>
-    <t>(4.939)</t>
-  </si>
-  <si>
-    <t>5.565</t>
-  </si>
-  <si>
-    <t>(6.687)</t>
-  </si>
-  <si>
-    <t>0.796</t>
-  </si>
-  <si>
-    <t>(8.065)</t>
-  </si>
-  <si>
-    <t>-7.692</t>
-  </si>
-  <si>
-    <t>(6.467)</t>
-  </si>
-  <si>
-    <t>11.044</t>
-  </si>
-  <si>
-    <t>148.4</t>
-  </si>
-  <si>
-    <t>Carea | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t>63.680***</t>
-  </si>
-  <si>
-    <t>(2.815)</t>
-  </si>
-  <si>
-    <t>1.384</t>
-  </si>
-  <si>
-    <t>(3.981)</t>
-  </si>
-  <si>
-    <t>0.233</t>
-  </si>
-  <si>
-    <t>(5.266)</t>
-  </si>
-  <si>
-    <t>-2.826</t>
-  </si>
-  <si>
-    <t>(3.812)</t>
-  </si>
-  <si>
-    <t>6.295</t>
-  </si>
-  <si>
-    <t>0.072</t>
-  </si>
-  <si>
-    <t>108.9</t>
-  </si>
-  <si>
-    <t>logLCCC | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t>6.170***</t>
-  </si>
-  <si>
-    <t>(0.004)</t>
-  </si>
-  <si>
-    <t>0.005</t>
-  </si>
-  <si>
-    <t>(0.005)</t>
-  </si>
-  <si>
-    <t>(0.006)</t>
-  </si>
-  <si>
-    <t>0.003</t>
-  </si>
-  <si>
-    <t>0.012</t>
-  </si>
-  <si>
-    <t>-155.4</t>
-  </si>
-  <si>
-    <t>logLCCC |1000 | Clarisia</t>
-  </si>
-  <si>
-    <t>6.043***</t>
-  </si>
-  <si>
-    <t>(0.018)</t>
-  </si>
-  <si>
-    <t>0.060</t>
-  </si>
-  <si>
-    <t>(0.037)</t>
-  </si>
-  <si>
-    <t>(0.024)</t>
-  </si>
-  <si>
-    <t>0.040</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>0.263</t>
-  </si>
-  <si>
-    <t>-16.6</t>
-  </si>
-  <si>
-    <t>logLCCC  | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t>6.194***</t>
-  </si>
-  <si>
-    <t>-0.005</t>
-  </si>
-  <si>
-    <t>(0.008)</t>
-  </si>
-  <si>
-    <t>0.001</t>
-  </si>
-  <si>
-    <t>-0.006</t>
-  </si>
-  <si>
-    <t>(0.007)</t>
-  </si>
-  <si>
-    <t>0.018</t>
-  </si>
-  <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>-183.4</t>
-  </si>
-  <si>
-    <t>logLCCC  | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t>6.158***</t>
-  </si>
-  <si>
-    <t>-0.003</t>
-  </si>
-  <si>
-    <t>-0.017*</t>
-  </si>
-  <si>
-    <t>0.017</t>
-  </si>
-  <si>
-    <t>0.119</t>
-  </si>
-  <si>
-    <t>-219.7</t>
-  </si>
-  <si>
-    <t>logLCCC  | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t>6.083***</t>
-  </si>
-  <si>
-    <t>-0.008</t>
-  </si>
-  <si>
-    <t>(0.010)</t>
-  </si>
-  <si>
-    <t>0.010</t>
-  </si>
-  <si>
-    <t>(0.012)</t>
-  </si>
-  <si>
-    <t>0.004</t>
-  </si>
-  <si>
-    <t>-71.4</t>
-  </si>
-  <si>
-    <t>logLCCC  | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t>6.096***</t>
-  </si>
-  <si>
-    <t>0.002</t>
-  </si>
-  <si>
-    <t>(0.015)</t>
-  </si>
-  <si>
-    <t>0.039+</t>
-  </si>
-  <si>
-    <t>(0.021)</t>
-  </si>
-  <si>
-    <t>0.009</t>
-  </si>
-  <si>
-    <t>0.024</t>
-  </si>
-  <si>
-    <t>0.215</t>
-  </si>
-  <si>
-    <t>0.310</t>
-  </si>
-  <si>
-    <t>-45.7</t>
-  </si>
-  <si>
-    <t>LPC | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t>0.650***</t>
-  </si>
-  <si>
-    <t>(0.051)</t>
-  </si>
-  <si>
-    <t>-0.012</t>
-  </si>
-  <si>
-    <t>(0.066)</t>
-  </si>
-  <si>
-    <t>0.078</t>
-  </si>
-  <si>
-    <t>(0.068)</t>
-  </si>
-  <si>
-    <t>0.123+</t>
-  </si>
-  <si>
-    <t>0.051</t>
-  </si>
-  <si>
-    <t>0.136</t>
-  </si>
-  <si>
-    <t>0.131</t>
-  </si>
-  <si>
-    <t>0.238</t>
-  </si>
-  <si>
-    <t>-14.2</t>
-  </si>
-  <si>
-    <t>LPC | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t>0.793***</t>
-  </si>
-  <si>
-    <t>0.169</t>
-  </si>
-  <si>
-    <t>(0.155)</t>
-  </si>
-  <si>
-    <t>0.359*</t>
-  </si>
-  <si>
-    <t>(0.103)</t>
-  </si>
-  <si>
-    <t>0.381**</t>
-  </si>
-  <si>
-    <t>0.609</t>
-  </si>
-  <si>
-    <t>6.5</t>
-  </si>
-  <si>
-    <t>LPC | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t>0.784***</t>
-  </si>
-  <si>
-    <t>(0.079)</t>
-  </si>
-  <si>
-    <t>-0.015</t>
-  </si>
-  <si>
-    <t>(0.094)</t>
-  </si>
-  <si>
-    <t>0.526***</t>
-  </si>
-  <si>
-    <t>(0.100)</t>
-  </si>
-  <si>
-    <t>0.449***</t>
-  </si>
-  <si>
-    <t>0.093</t>
-  </si>
-  <si>
-    <t>0.218</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>0.518</t>
-  </si>
-  <si>
-    <t>0.593</t>
-  </si>
-  <si>
-    <t>16.4</t>
-  </si>
-  <si>
-    <t>LPC | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t>0.434***</t>
-  </si>
-  <si>
-    <t>(0.099)</t>
-  </si>
-  <si>
-    <t>(0.157)</t>
-  </si>
-  <si>
-    <t>0.444**</t>
-  </si>
-  <si>
-    <t>(0.146)</t>
-  </si>
-  <si>
-    <t>1.263***</t>
-  </si>
-  <si>
-    <t>(0.149)</t>
-  </si>
-  <si>
-    <t>0.384</t>
-  </si>
-  <si>
-    <t>0.643</t>
-  </si>
-  <si>
-    <t>64.6</t>
-  </si>
-  <si>
-    <t>LPC | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t>0.835***</t>
-  </si>
-  <si>
-    <t>-0.034</t>
-  </si>
-  <si>
-    <t>(0.151)</t>
-  </si>
-  <si>
-    <t>0.235</t>
-  </si>
-  <si>
-    <t>(0.182)</t>
-  </si>
-  <si>
-    <t>0.581**</t>
-  </si>
-  <si>
-    <t>0.250</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>0.542</t>
-  </si>
-  <si>
-    <t>19.3</t>
-  </si>
-  <si>
-    <t>LPC | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t>0.559***</t>
-  </si>
-  <si>
-    <t>(0.119)</t>
-  </si>
-  <si>
-    <t>(0.168)</t>
-  </si>
-  <si>
-    <t>0.161</t>
-  </si>
-  <si>
-    <t>(0.223)</t>
-  </si>
-  <si>
-    <t>1.077***</t>
-  </si>
-  <si>
-    <t>0.266</t>
-  </si>
-  <si>
-    <t>0.781</t>
-  </si>
-  <si>
-    <t>20.4</t>
-  </si>
-  <si>
-    <t>logLPC | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t>-0.446***</t>
-  </si>
-  <si>
-    <t>(0.076)</t>
-  </si>
-  <si>
-    <t>-0.038</t>
-  </si>
-  <si>
-    <t>0.121</t>
-  </si>
-  <si>
-    <t>(0.096)</t>
-  </si>
-  <si>
-    <t>0.178+</t>
-  </si>
-  <si>
-    <t>0.086</t>
-  </si>
-  <si>
-    <t>0.189</t>
-  </si>
-  <si>
-    <t>0.153</t>
-  </si>
-  <si>
-    <t>7.5</t>
-  </si>
-  <si>
-    <t>logLPC | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t>-0.233*</t>
-  </si>
-  <si>
-    <t>(0.067)</t>
-  </si>
-  <si>
-    <t>(0.134)</t>
-  </si>
-  <si>
-    <t>0.370**</t>
-  </si>
-  <si>
-    <t>(0.088)</t>
-  </si>
-  <si>
-    <t>0.386**</t>
-  </si>
-  <si>
-    <t>0.116</t>
-  </si>
-  <si>
-    <t>0.684</t>
-  </si>
-  <si>
-    <t>4.1</t>
-  </si>
-  <si>
-    <t>logLPC | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t>-0.257**</t>
-  </si>
-  <si>
-    <t>(0.081)</t>
-  </si>
-  <si>
-    <t>-0.019</t>
-  </si>
-  <si>
-    <t>(0.092)</t>
-  </si>
-  <si>
-    <t>0.489***</t>
-  </si>
-  <si>
-    <t>(0.098)</t>
-  </si>
-  <si>
-    <t>0.428***</t>
-  </si>
-  <si>
-    <t>(0.085)</t>
-  </si>
-  <si>
-    <t>0.213</t>
-  </si>
-  <si>
-    <t>0.491</t>
-  </si>
-  <si>
-    <t>0.592</t>
-  </si>
-  <si>
-    <t>14.9</t>
-  </si>
-  <si>
-    <t>logLPC | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t>-0.883***</t>
-  </si>
-  <si>
-    <t>(0.090)</t>
-  </si>
-  <si>
-    <t>0.027</t>
-  </si>
-  <si>
-    <t>(0.143)</t>
-  </si>
-  <si>
-    <t>0.687***</t>
-  </si>
-  <si>
-    <t>(0.132)</t>
-  </si>
-  <si>
-    <t>1.315***</t>
-  </si>
-  <si>
-    <t>(0.135)</t>
-  </si>
-  <si>
-    <t>0.349</t>
-  </si>
-  <si>
-    <t>0.707</t>
-  </si>
-  <si>
-    <t>55.8</t>
-  </si>
-  <si>
-    <t>logLPC | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t>-0.183*</t>
-  </si>
-  <si>
-    <t>(0.082)</t>
-  </si>
-  <si>
-    <t>-0.039</t>
-  </si>
-  <si>
-    <t>(0.111)</t>
-  </si>
-  <si>
-    <t>0.249+</t>
-  </si>
-  <si>
-    <t>0.492***</t>
-  </si>
-  <si>
-    <t>0.183</t>
-  </si>
-  <si>
-    <t>0.622</t>
-  </si>
-  <si>
-    <t>9.4</t>
-  </si>
-  <si>
-    <t>logLPC | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t>-0.585***</t>
-  </si>
-  <si>
-    <t>(0.086)</t>
-  </si>
-  <si>
-    <t>0.081</t>
-  </si>
-  <si>
-    <t>(0.122)</t>
-  </si>
-  <si>
-    <t>0.255</t>
-  </si>
-  <si>
-    <t>(0.162)</t>
-  </si>
-  <si>
-    <t>1.043***</t>
-  </si>
-  <si>
-    <t>(0.117)</t>
-  </si>
-  <si>
-    <t>0.193</t>
-  </si>
-  <si>
-    <t>0.858</t>
-  </si>
-  <si>
-    <t>11.4</t>
-  </si>
-  <si>
-    <t>Parea | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t>0.081***</t>
-  </si>
-  <si>
-    <t>0.011+</t>
-  </si>
-  <si>
-    <t>0.018**</t>
-  </si>
-  <si>
-    <t>0.279</t>
-  </si>
-  <si>
-    <t>0.380</t>
-  </si>
-  <si>
-    <t>-170.3</t>
-  </si>
-  <si>
-    <t>Parea | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t>0.087***</t>
-  </si>
-  <si>
-    <t>0.022+</t>
-  </si>
-  <si>
-    <t>(0.011)</t>
-  </si>
-  <si>
-    <t>0.033*</t>
-  </si>
-  <si>
-    <t>0.008</t>
-  </si>
-  <si>
-    <t>0.015</t>
-  </si>
-  <si>
-    <t>0.437</t>
-  </si>
-  <si>
-    <t>0.579</t>
-  </si>
-  <si>
-    <t>-27.6</t>
-  </si>
-  <si>
-    <t>Parea | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t>0.221***</t>
-  </si>
-  <si>
-    <t>0.167**</t>
-  </si>
-  <si>
-    <t>(0.056)</t>
-  </si>
-  <si>
-    <t>0.174***</t>
-  </si>
-  <si>
-    <t>(0.047)</t>
-  </si>
-  <si>
-    <t>0.011</t>
-  </si>
-  <si>
-    <t>0.345</t>
-  </si>
-  <si>
-    <t>0.351</t>
-  </si>
-  <si>
-    <t>-34.5</t>
-  </si>
-  <si>
-    <t>Parea | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t>0.122***</t>
-  </si>
-  <si>
-    <t>(0.033)</t>
-  </si>
-  <si>
-    <t>-0.001</t>
-  </si>
-  <si>
-    <t>0.122*</t>
-  </si>
-  <si>
-    <t>(0.048)</t>
-  </si>
-  <si>
-    <t>0.382***</t>
-  </si>
-  <si>
-    <t>(0.049)</t>
-  </si>
-  <si>
-    <t>0.126</t>
-  </si>
-  <si>
-    <t>0.604</t>
-  </si>
-  <si>
-    <t>-38.1</t>
-  </si>
-  <si>
-    <t>Parea | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t>0.125***</t>
-  </si>
-  <si>
-    <t>(0.027)</t>
-  </si>
-  <si>
-    <t>(0.044)</t>
-  </si>
-  <si>
-    <t>0.093*</t>
-  </si>
-  <si>
-    <t>(0.035)</t>
-  </si>
-  <si>
-    <t>0.319</t>
-  </si>
-  <si>
-    <t>-29.1</t>
-  </si>
-  <si>
-    <t>Parea | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t>0.080***</t>
-  </si>
-  <si>
-    <t>(0.016)</t>
-  </si>
-  <si>
-    <t>(0.023)</t>
-  </si>
-  <si>
-    <t>0.020</t>
-  </si>
-  <si>
-    <t>0.145***</t>
-  </si>
-  <si>
-    <t>(0.022)</t>
-  </si>
-  <si>
-    <t>0.778</t>
-  </si>
-  <si>
-    <t>-35.7</t>
-  </si>
-  <si>
-    <t>Leaf N:P | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t>24.474***</t>
-  </si>
-  <si>
-    <t>(1.600)</t>
-  </si>
-  <si>
-    <t>1.444</t>
-  </si>
-  <si>
-    <t>(2.188)</t>
-  </si>
-  <si>
-    <t>-1.987</t>
-  </si>
-  <si>
-    <t>(2.331)</t>
-  </si>
-  <si>
-    <t>-2.163</t>
-  </si>
-  <si>
-    <t>(2.223)</t>
-  </si>
-  <si>
-    <t>1.168</t>
-  </si>
-  <si>
-    <t>4.690</t>
-  </si>
-  <si>
-    <t>0.087</t>
-  </si>
-  <si>
-    <t>0.140</t>
-  </si>
-  <si>
-    <t>211.6</t>
-  </si>
-  <si>
-    <t>Leaf N:P | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t>21.867***</t>
-  </si>
-  <si>
-    <t>(1.675)</t>
-  </si>
-  <si>
-    <t>-0.995</t>
-  </si>
-  <si>
-    <t>(3.323)</t>
-  </si>
-  <si>
-    <t>-1.076</t>
-  </si>
-  <si>
-    <t>(2.186)</t>
-  </si>
-  <si>
-    <t>-4.953+</t>
-  </si>
-  <si>
-    <t>(2.198)</t>
-  </si>
-  <si>
-    <t>0.488</t>
-  </si>
-  <si>
-    <t>2.859</t>
-  </si>
-  <si>
-    <t>0.356</t>
-  </si>
-  <si>
-    <t>0.374</t>
-  </si>
-  <si>
-    <t>55.5</t>
-  </si>
-  <si>
-    <t>Leaf N:P | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t>15.015***</t>
-  </si>
-  <si>
-    <t>(0.948)</t>
-  </si>
-  <si>
-    <t>2.175*</t>
-  </si>
-  <si>
-    <t>(0.897)</t>
-  </si>
-  <si>
-    <t>-5.308***</t>
-  </si>
-  <si>
-    <t>(0.953)</t>
-  </si>
-  <si>
-    <t>-5.939***</t>
-  </si>
-  <si>
-    <t>(0.810)</t>
-  </si>
-  <si>
-    <t>1.467</t>
-  </si>
-  <si>
-    <t>2.071</t>
-  </si>
-  <si>
-    <t>0.653</t>
-  </si>
-  <si>
-    <t>0.769</t>
-  </si>
-  <si>
-    <t>203.1</t>
-  </si>
-  <si>
-    <t>Leaf N:P | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t>23.224***</t>
-  </si>
-  <si>
-    <t>(1.132)</t>
-  </si>
-  <si>
-    <t>0.308</t>
-  </si>
-  <si>
-    <t>(1.582)</t>
-  </si>
-  <si>
-    <t>-11.021***</t>
-  </si>
-  <si>
-    <t>(1.492)</t>
-  </si>
-  <si>
-    <t>-16.982***</t>
-  </si>
-  <si>
-    <t>(1.508)</t>
-  </si>
-  <si>
-    <t>1.048</t>
-  </si>
-  <si>
-    <t>3.874</t>
-  </si>
-  <si>
-    <t>0.772</t>
-  </si>
-  <si>
-    <t>0.788</t>
-  </si>
-  <si>
-    <t>279.1</t>
-  </si>
-  <si>
-    <t>Leaf N:P | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t>17.046***</t>
-  </si>
-  <si>
-    <t>(1.615)</t>
-  </si>
-  <si>
-    <t>4.648*</t>
-  </si>
-  <si>
-    <t>(2.036)</t>
-  </si>
-  <si>
-    <t>-1.420</t>
-  </si>
-  <si>
-    <t>(2.453)</t>
-  </si>
-  <si>
-    <t>-6.056**</t>
-  </si>
-  <si>
-    <t>(1.961)</t>
-  </si>
-  <si>
-    <t>1.197</t>
-  </si>
-  <si>
-    <t>3.337</t>
-  </si>
-  <si>
-    <t>0.599</t>
-  </si>
-  <si>
-    <t>0.645</t>
-  </si>
-  <si>
-    <t>109.1</t>
-  </si>
-  <si>
-    <t>Leaf N:P | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t>18.652***</t>
-  </si>
-  <si>
-    <t>(1.117)</t>
-  </si>
-  <si>
-    <t>(1.580)</t>
-  </si>
-  <si>
-    <t>-3.078</t>
-  </si>
-  <si>
-    <t>(2.090)</t>
-  </si>
-  <si>
-    <t>-11.345***</t>
-  </si>
-  <si>
-    <t>(1.513)</t>
-  </si>
-  <si>
-    <t>0.823</t>
-  </si>
-  <si>
-    <t>83.1</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="739">
+  <si>
+    <t xml:space="preserve">Modelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimates.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimates.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimates.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimates.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimates.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimates.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimates.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimates.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimates.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gof.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gof.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gof.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">term</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUBN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUBNP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD (Intercept Bloque)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD (Observations)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num.Obs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R2 Marg.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R2 Cond.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">statistic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">std.error</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Nmass | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.336***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.480)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.579)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.592)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.320*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.561)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nmass | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.393***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.314)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.629)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.259*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.739)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nmass | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.606***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.448)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.533*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.665)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.708)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.601)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nmass | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.812***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.287)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.192**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.386)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.909*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.366)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.369)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nmass | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.134***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.119)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.403*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.180)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.589+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.421)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.131)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nmass | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.434***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.699)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.989)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.308)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.947)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logNmass | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.728***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.030)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.036)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.082*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.034)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-54.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logNmass | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.849***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.070)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.141)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.093)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logNmass | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.442***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.039)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.058)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.061)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-26.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logNmass | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.168***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.032)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.043)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.041)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.071+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-52.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logNmass | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.648***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.065)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.201**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.078)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.062)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logNmass | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.338***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.064)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.091)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.121)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.087)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narea | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.920***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.075)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.108)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.120)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.250*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.115)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narea | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.892***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.112)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narea | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.272***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.161)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.231)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.247)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.209)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narea | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.882***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.260)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.410)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.380)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.389)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narea | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.136***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.170)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.702**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.222)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.268)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.214)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narea | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.484***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.102)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.144)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.191)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.138)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmass | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">478.002***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.864)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.637)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.819)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.718)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmass | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.372***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.884)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(15.767)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10.429)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmass | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">489.936***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.460)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.649)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.054)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.353)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmass | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">472.530***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.366)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.836*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.124)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.157)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmass | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">438.175***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.416)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.459)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.373)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.301)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmass | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">444.044***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.317)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.780)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.429+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9.040)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.503)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carea | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.501***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.765)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.434)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.261)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carea | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.093***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.463)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.463*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.642)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.063*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.656)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.759)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carea | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.527***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.780)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.588)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8.078)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.856)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carea | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.985***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.549)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.612)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.209)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.324)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">393.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carea | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.582***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.939)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.687)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8.065)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.467)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carea | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.680***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.815)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.981)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.266)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.812)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLCCC | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.170***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.004)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.005)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-155.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLCCC |1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.043***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.018)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.037)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-16.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLCCC  | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.194***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-183.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLCCC  | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.158***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.017*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-219.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLCCC  | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.083***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.010)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.012)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-71.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLCCC  | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.096***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.015)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.039+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.021)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-45.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.650***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.066)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.068)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-14.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.793***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.155)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.103)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.079)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.094)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.526***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.099)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.157)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.444**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.263***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.149)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.151)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.182)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.119)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.168)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.223)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.077***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.446***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.076)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.096)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.178+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.233*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.067)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.134)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.088)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.257**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.081)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.092)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.098)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.085)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.883***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.090)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.143)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.687***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.132)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.315***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.135)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.183*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.082)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.111)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.249+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.585***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.086)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.122)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.162)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.043***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.117)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parea | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.081***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.011+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.018**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-170.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parea | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.087***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.022+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.011)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.033*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-27.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parea | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.221***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.056)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.174***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.047)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-34.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parea | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.033)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.048)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.049)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-38.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parea | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.027)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.044)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.093*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.035)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-29.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parea | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.080***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.016)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.022)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-35.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leaf N:P | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.474***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.600)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.188)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.331)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.223)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leaf N:P | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.867***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.675)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.186)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.953+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.198)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leaf N:P | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.015***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.948)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.175*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.897)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.308***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.953)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.939***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.810)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leaf N:P | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.224***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.132)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.582)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-11.021***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.492)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-16.982***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.508)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">279.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leaf N:P | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.046***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.615)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.648*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.036)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.453)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.056**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.961)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leaf N:P | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.652***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.117)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.580)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.090)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-11.345***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.513)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2278,20 +2272,11 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:O63" totalsRowShown="0">
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:O63" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A1:O63"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Modelo"/>
@@ -2592,14 +2577,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28.5703125" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2646,7 +2628,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -2693,7 +2675,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -2740,7 +2722,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -2787,7 +2769,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -2834,7 +2816,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>58</v>
       </c>
@@ -2881,7 +2863,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>71</v>
       </c>
@@ -2928,7 +2910,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>86</v>
       </c>
@@ -2975,7 +2957,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>101</v>
       </c>
@@ -3022,7 +3004,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>114</v>
       </c>
@@ -3069,7 +3051,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>127</v>
       </c>
@@ -3116,7 +3098,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>138</v>
       </c>
@@ -3163,7 +3145,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>149</v>
       </c>
@@ -3210,7 +3192,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>162</v>
       </c>
@@ -3257,7 +3239,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>175</v>
       </c>
@@ -3304,7 +3286,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>186</v>
       </c>
@@ -3351,7 +3333,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>198</v>
       </c>
@@ -3398,7 +3380,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>209</v>
       </c>
@@ -3445,7 +3427,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>221</v>
       </c>
@@ -3492,7 +3474,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>236</v>
       </c>
@@ -3539,7 +3521,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>250</v>
       </c>
@@ -3586,7 +3568,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>261</v>
       </c>
@@ -3633,7 +3615,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>274</v>
       </c>
@@ -3680,7 +3662,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
         <v>285</v>
       </c>
@@ -3727,7 +3709,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" t="s">
         <v>298</v>
       </c>
@@ -3774,7 +3756,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" t="s">
         <v>312</v>
       </c>
@@ -3821,7 +3803,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" t="s">
         <v>325</v>
       </c>
@@ -3868,7 +3850,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" t="s">
         <v>339</v>
       </c>
@@ -3915,7 +3897,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>351</v>
       </c>
@@ -3962,7 +3944,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" t="s">
         <v>365</v>
       </c>
@@ -4009,7 +3991,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" t="s">
         <v>379</v>
       </c>
@@ -4056,7 +4038,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" t="s">
         <v>390</v>
       </c>
@@ -4103,7 +4085,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" t="s">
         <v>401</v>
       </c>
@@ -4150,7 +4132,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" t="s">
         <v>413</v>
       </c>
@@ -4197,7 +4179,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35" t="s">
         <v>422</v>
       </c>
@@ -4244,7 +4226,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36" t="s">
         <v>432</v>
       </c>
@@ -4291,7 +4273,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" t="s">
         <v>442</v>
       </c>
@@ -4338,7 +4320,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38" t="s">
         <v>449</v>
       </c>
@@ -4385,7 +4367,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39" t="s">
         <v>457</v>
       </c>
@@ -4432,7 +4414,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40" t="s">
         <v>468</v>
       </c>
@@ -4479,7 +4461,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" t="s">
         <v>481</v>
       </c>
@@ -4526,7 +4508,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42" t="s">
         <v>490</v>
       </c>
@@ -4573,7 +4555,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43" t="s">
         <v>504</v>
       </c>
@@ -4620,7 +4602,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44" t="s">
         <v>515</v>
       </c>
@@ -4667,7 +4649,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45" t="s">
         <v>526</v>
       </c>
@@ -4714,7 +4696,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46" t="s">
         <v>536</v>
       </c>
@@ -4761,7 +4743,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47" t="s">
         <v>547</v>
       </c>
@@ -4808,7 +4790,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="A48" t="s">
         <v>557</v>
       </c>
@@ -4855,7 +4837,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="A49" t="s">
         <v>570</v>
       </c>
@@ -4902,7 +4884,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50" t="s">
         <v>582</v>
       </c>
@@ -4949,7 +4931,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="A51" t="s">
         <v>592</v>
       </c>
@@ -4996,7 +4978,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="A52" t="s">
         <v>604</v>
       </c>
@@ -5043,7 +5025,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="A53" t="s">
         <v>611</v>
       </c>
@@ -5090,7 +5072,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="A54" t="s">
         <v>621</v>
       </c>
@@ -5137,7 +5119,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="A55" t="s">
         <v>631</v>
       </c>
@@ -5184,7 +5166,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="A56" t="s">
         <v>642</v>
       </c>
@@ -5231,7 +5213,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="A57" t="s">
         <v>650</v>
       </c>
@@ -5278,7 +5260,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="A58" t="s">
         <v>659</v>
       </c>
@@ -5325,7 +5307,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59" t="s">
         <v>673</v>
       </c>
@@ -5372,7 +5354,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="A60" t="s">
         <v>687</v>
       </c>
@@ -5419,7 +5401,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61">
       <c r="A61" t="s">
         <v>701</v>
       </c>
@@ -5466,7 +5448,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62">
       <c r="A62" t="s">
         <v>715</v>
       </c>
@@ -5513,7 +5495,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63">
       <c r="A63" t="s">
         <v>729</v>
       </c>
@@ -5562,9 +5544,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/NUMEX_pre_RStudio/models_est.xlsx
+++ b/NUMEX_pre_RStudio/models_est.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="733">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">(Intercept)</t>
   </si>
   <si>
-    <t xml:space="preserve">SUBN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUBNP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUBP</t>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N × P</t>
   </si>
   <si>
     <t xml:space="preserve">SD (Intercept Bloque)</t>
@@ -119,18 +119,18 @@
     <t xml:space="preserve">(0.579)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.780</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.592)</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.320*</t>
   </si>
   <si>
     <t xml:space="preserve">(0.561)</t>
   </si>
   <si>
+    <t xml:space="preserve">-0.871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.846)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.562</t>
   </si>
   <si>
@@ -164,13 +164,16 @@
     <t xml:space="preserve">(2.629)</t>
   </si>
   <si>
-    <t xml:space="preserve">6.259*</t>
+    <t xml:space="preserve">2.227</t>
   </si>
   <si>
     <t xml:space="preserve">(1.739)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.227</t>
+    <t xml:space="preserve">1.365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.083)</t>
   </si>
   <si>
     <t xml:space="preserve">0.000</t>
@@ -203,18 +206,18 @@
     <t xml:space="preserve">(0.665)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.708)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-0.508</t>
   </si>
   <si>
     <t xml:space="preserve">(0.601)</t>
   </si>
   <si>
+    <t xml:space="preserve">-0.596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.951)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.552</t>
   </si>
   <si>
@@ -242,18 +245,18 @@
     <t xml:space="preserve">(0.386)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.909*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.366)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-0.619</t>
   </si>
   <si>
     <t xml:space="preserve">(0.369)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.540)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.280</t>
   </si>
   <si>
@@ -287,18 +290,18 @@
     <t xml:space="preserve">(1.180)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.589+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.421)</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.359</t>
   </si>
   <si>
     <t xml:space="preserve">(1.131)</t>
   </si>
   <si>
+    <t xml:space="preserve">-2.174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.778)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.417</t>
   </si>
   <si>
@@ -332,18 +335,18 @@
     <t xml:space="preserve">(0.989)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.308)</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.297</t>
   </si>
   <si>
     <t xml:space="preserve">(0.947)</t>
   </si>
   <si>
+    <t xml:space="preserve">-0.590</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.615)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.563</t>
   </si>
   <si>
@@ -371,15 +374,18 @@
     <t xml:space="preserve">(0.036)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.049</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.082*</t>
   </si>
   <si>
     <t xml:space="preserve">(0.034)</t>
   </si>
   <si>
+    <t xml:space="preserve">-0.054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.052)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.038</t>
   </si>
   <si>
@@ -410,13 +416,16 @@
     <t xml:space="preserve">(0.141)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313*</t>
+    <t xml:space="preserve">0.120</t>
   </si>
   <si>
     <t xml:space="preserve">(0.093)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.120</t>
+    <t xml:space="preserve">0.043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.165)</t>
   </si>
   <si>
     <t xml:space="preserve">0.122</t>
@@ -443,13 +452,13 @@
     <t xml:space="preserve">(0.058)</t>
   </si>
   <si>
-    <t xml:space="preserve">(0.061)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-0.043</t>
   </si>
   <si>
-    <t xml:space="preserve">(0.052)</t>
+    <t xml:space="preserve">-0.044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.082)</t>
   </si>
   <si>
     <t xml:space="preserve">0.134</t>
@@ -476,13 +485,16 @@
     <t xml:space="preserve">(0.043)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102*</t>
+    <t xml:space="preserve">-0.071+</t>
   </si>
   <si>
     <t xml:space="preserve">(0.041)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.071+</t>
+    <t xml:space="preserve">0.041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.060)</t>
   </si>
   <si>
     <t xml:space="preserve">0.031</t>
@@ -512,1386 +524,1386 @@
     <t xml:space="preserve">0.201**</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163+</t>
+    <t xml:space="preserve">0.088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.062)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.098)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logNmass | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.338***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.064)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.091)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.087)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.149)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narea | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.920***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.075)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.108)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.250*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.115)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.168)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narea | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.892***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.112)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.224)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narea | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.272***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.161)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.231)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.209)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.331)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narea | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.429***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.080)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.401***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.101)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.097)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.142)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narea | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.136***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.170)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.702**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.222)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.214)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.336)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narea | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.484***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.102)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.144)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.138)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.236)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmass | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">478.002***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.864)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.637)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.718)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.916)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmass | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.372***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.884)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(15.767)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10.429)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-33.621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(18.489)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmass | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">489.936***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.460)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.649)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.353)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.374)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmass | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">472.530***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.366)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.312)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.157)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.666)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmass | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">438.175***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.416)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.459)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.301)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.746)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmass | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">444.044***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.317)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.780)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.503)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11.017)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carea | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.791***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.763)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.908)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.028)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.803)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">225.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carea | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.093***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.463)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.463*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.642)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.759)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.381)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carea | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.567***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.601)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.339)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.766)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10.855)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carea | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.985***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.549)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.612)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.324)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9.664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.860)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">393.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carea | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.582***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.939)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.687)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.467)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10.139)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carea | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.680***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.815)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.981)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.812)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.501)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLCCC | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.170***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.004)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.005)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-155.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLCCC |1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.043***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.018)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.037)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-16.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLCCC  | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.194***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.011)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-183.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLCCC  | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.158***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.010)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-219.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLCCC  | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.083***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.015)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-71.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLCCC  | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.096***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.012)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-45.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.650***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.066)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-14.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.793***</t>
   </si>
   <si>
     <t xml:space="preserve">(0.078)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.062)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logNmass | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.338***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.064)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.091)</t>
+    <t xml:space="preserve">0.169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.155)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.103)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.182)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.784***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.079)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.094)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.449***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.136)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.434***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.099)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.157)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.263***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.811***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.220)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.835***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.151)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.581**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.119)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.077***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.963**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.275)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.446***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.076)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.178+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.137)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.233*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.067)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.134)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.386**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.088)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.257**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.081)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.092)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.085)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.132)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.883***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.090)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.143)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.315***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.135)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.655**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.200)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.183*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.111)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.171)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.585***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.086)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.122)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.043***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.117)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.869***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parea | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.081***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.018**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.009)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-170.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parea | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.087***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.033*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.022)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-27.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parea | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.222***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.033)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.047)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.019</t>
   </si>
   <si>
     <t xml:space="preserve">0.076</t>
   </si>
   <si>
-    <t xml:space="preserve">(0.121)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.087)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narea | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.920***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.075)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.108)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.120)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.250*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.115)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narea | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.892***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.112)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.224)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narea | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.272***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.161)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.231)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.247)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.209)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narea | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.429***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.080)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.401***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.101)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.096)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.097)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narea | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.136***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.170)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.702**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.222)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.268)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.214)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narea | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.484***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.102)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.144)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.191)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.138)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmass | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">478.002***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.864)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.637)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.819)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.718)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmass | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.372***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.884)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(15.767)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(10.429)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmass | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">489.936***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.460)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.649)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.054)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.353)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmass | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">472.530***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.366)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.312)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.836*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.124)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.157)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmass | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">438.175***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.416)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.459)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.373)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.301)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmass | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">444.044***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.317)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.780)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.429+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9.040)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.503)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carea | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.791***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.763)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.908)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.177)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.028)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">225.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carea | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.093***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.463)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.463*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.642)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.063*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.656)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.759)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carea | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.567***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.601)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7.339)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8.161)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.766)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carea | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.985***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.549)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.612)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.209)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.324)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">393.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carea | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.582***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.939)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.687)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8.065)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.467)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carea | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.680***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.815)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.981)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.266)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.812)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLCCC | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.170***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.004)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.005)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-155.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLCCC |1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.043***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.018)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.037)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.024)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-16.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLCCC  | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.194***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-183.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLCCC  | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.158***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.017*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-219.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLCCC  | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.083***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.010)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-71.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLCCC  | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.096***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.015)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.039+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.021)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-45.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.650***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.066)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.068)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-14.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.793***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.155)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.103)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.784***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.079)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.094)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.526***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.100)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.434***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.099)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.157)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.444**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.263***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.149)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.835***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.151)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.182)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.581**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.119)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.168)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.223)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.077***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.446***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.076)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.178+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.233*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.067)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.134)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.088)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.257**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.081)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.092)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.098)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.085)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.883***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.090)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.143)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.132)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.315***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.135)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.183*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.082)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.111)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.249+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.585***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.086)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.122)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.162)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.043***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.117)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parea | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.081***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.011+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.018**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-170.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parea | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.087***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.022+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.033*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-27.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parea | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.222***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.033)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.035)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.019</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.485</t>
   </si>
   <si>
@@ -1910,18 +1922,18 @@
     <t xml:space="preserve">-0.001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.122*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.048)</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.382***</t>
   </si>
   <si>
     <t xml:space="preserve">(0.049)</t>
   </si>
   <si>
+    <t xml:space="preserve">-0.258***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.072)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.126</t>
   </si>
   <si>
@@ -1937,9 +1949,6 @@
     <t xml:space="preserve">0.125***</t>
   </si>
   <si>
-    <t xml:space="preserve">(0.029)</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.063*</t>
   </si>
   <si>
@@ -1961,13 +1970,10 @@
     <t xml:space="preserve">(0.023)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.020</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.145***</t>
   </si>
   <si>
-    <t xml:space="preserve">(0.022)</t>
+    <t xml:space="preserve">-0.134**</t>
   </si>
   <si>
     <t xml:space="preserve">0.778</t>
@@ -1991,18 +1997,18 @@
     <t xml:space="preserve">(2.188)</t>
   </si>
   <si>
-    <t xml:space="preserve">-1.987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.331)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-2.163</t>
   </si>
   <si>
     <t xml:space="preserve">(2.223)</t>
   </si>
   <si>
+    <t xml:space="preserve">-1.269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.290)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.168</t>
   </si>
   <si>
@@ -2033,18 +2039,18 @@
     <t xml:space="preserve">(3.323)</t>
   </si>
   <si>
-    <t xml:space="preserve">-1.076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.186)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-4.953+</t>
   </si>
   <si>
     <t xml:space="preserve">(2.198)</t>
   </si>
   <si>
+    <t xml:space="preserve">4.873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.932)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.488</t>
   </si>
   <si>
@@ -2075,18 +2081,18 @@
     <t xml:space="preserve">(0.840)</t>
   </si>
   <si>
-    <t xml:space="preserve">-5.306***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.893)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-5.550***</t>
   </si>
   <si>
     <t xml:space="preserve">(0.773)</t>
   </si>
   <si>
+    <t xml:space="preserve">-1.908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.212)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.326</t>
   </si>
   <si>
@@ -2117,18 +2123,18 @@
     <t xml:space="preserve">(1.594)</t>
   </si>
   <si>
-    <t xml:space="preserve">-10.627***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.505)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-16.578***</t>
   </si>
   <si>
     <t xml:space="preserve">(1.525)</t>
   </si>
   <si>
+    <t xml:space="preserve">5.278*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.230)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.972</t>
   </si>
   <si>
@@ -2159,15 +2165,15 @@
     <t xml:space="preserve">(1.938)</t>
   </si>
   <si>
-    <t xml:space="preserve">-1.235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.338)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-5.020*</t>
   </si>
   <si>
+    <t xml:space="preserve">-0.826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.980)</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.201</t>
   </si>
   <si>
@@ -2189,16 +2195,16 @@
     <t xml:space="preserve">(1.580)</t>
   </si>
   <si>
-    <t xml:space="preserve">-3.078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2.090)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-11.345***</t>
   </si>
   <si>
     <t xml:space="preserve">(1.513)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.033**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.580)</t>
   </si>
   <si>
     <t xml:space="preserve">0.823</t>
@@ -2771,2751 +2777,2751 @@
         <v>52</v>
       </c>
       <c r="I5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N5" t="s">
         <v>29</v>
       </c>
       <c r="O5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N6" t="s">
         <v>29</v>
       </c>
       <c r="O6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" t="s">
         <v>29</v>
       </c>
       <c r="O9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L10" t="s">
         <v>41</v>
       </c>
       <c r="M10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="N10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="O10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K11" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M11" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="N11" t="s">
         <v>29</v>
       </c>
       <c r="O11" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B12" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C12" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E12" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F12" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="G12" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="H12" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I12" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K12" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M12" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N12" t="s">
         <v>29</v>
       </c>
       <c r="O12" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C13" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D13" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E13" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F13" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G13" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I13" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J13" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="K13" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="L13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M13" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="O13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C14" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D14" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E14" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F14" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G14" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H14" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="I14" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J14" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="K14" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="L14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M14" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="N14" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="O14" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D15" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E15" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F15" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G15" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H15" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I15" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="J15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K15" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="L15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N15" t="s">
         <v>29</v>
       </c>
       <c r="O15" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C16" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D16" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E16" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F16" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G16" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H16" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I16" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="J16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K16" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="L16" t="s">
         <v>41</v>
       </c>
       <c r="M16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="N16" t="s">
         <v>29</v>
       </c>
       <c r="O16" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C17" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D17" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E17" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="F17" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G17" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H17" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I17" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="J17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K17" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M17" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="N17" t="s">
         <v>29</v>
       </c>
       <c r="O17" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C18" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="D18" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E18" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="F18" t="s">
-        <v>172</v>
+        <v>219</v>
       </c>
       <c r="G18" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="H18" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="I18" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="J18" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="K18" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="L18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M18" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="N18" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="O18" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B19" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C19" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D19" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E19" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F19" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="G19" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="H19" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="I19" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="J19" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="K19" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="L19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="N19" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="O19" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B20" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C20" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D20" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E20" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F20" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="G20" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="H20" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="I20" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="J20" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="K20" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="L20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M20" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="N20" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="O20" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B21" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C21" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="D21" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E21" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="F21" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="G21" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="H21" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="I21" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="J21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K21" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="L21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M21" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="N21" t="s">
         <v>29</v>
       </c>
       <c r="O21" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B22" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C22" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D22" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E22" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="F22" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="G22" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="H22" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="I22" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="J22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K22" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="L22" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="M22" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="N22" t="s">
         <v>29</v>
       </c>
       <c r="O22" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B23" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C23" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D23" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E23" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="F23" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="G23" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="H23" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="I23" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="J23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K23" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="L23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M23" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="N23" t="s">
         <v>29</v>
       </c>
       <c r="O23" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B24" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C24" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="E24" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="F24" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="G24" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="H24" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="I24" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="J24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K24" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="L24" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="M24" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="N24" t="s">
         <v>29</v>
       </c>
       <c r="O24" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B25" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C25" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="D25" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="E25" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="F25" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="G25" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="H25" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="I25" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="J25" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="K25" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="L25" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="M25" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="N25" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="O25" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B26" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C26" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D26" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="E26" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="F26" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="G26" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="H26" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="I26" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J26" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="K26" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="L26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M26" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="N26" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="O26" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B27" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C27" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="D27" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="E27" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="F27" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="G27" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="H27" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="I27" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="J27" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="K27" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="L27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M27" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="N27" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="O27" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="B28" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="C28" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="D28" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E28" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F28" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="G28" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="H28" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="I28" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="J28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K28" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="L28" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="M28" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="N28" t="s">
         <v>29</v>
       </c>
       <c r="O28" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B29" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="C29" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="D29" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="E29" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="F29" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="G29" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="H29" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="I29" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="J29" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="K29" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="L29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M29" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="N29" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="O29" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="B30" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="C30" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="D30" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="E30" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="F30" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="G30" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="H30" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="I30" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="J30" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="K30" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="L30" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="M30" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="N30" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="O30" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="B31" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C31" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="D31" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="E31" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="F31" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="G31" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="H31" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="I31" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="J31" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K31" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="L31" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="M31" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="N31" t="s">
         <v>29</v>
       </c>
       <c r="O31" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B32" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="C32" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="D32" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="E32" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="F32" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="G32" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="H32" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="I32" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="J32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K32" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="L32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="N32" t="s">
         <v>29</v>
       </c>
       <c r="O32" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="B33" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C33" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D33" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="E33" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="F33" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="G33" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="H33" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="I33" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="J33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K33" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="L33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M33" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="N33" t="s">
         <v>29</v>
       </c>
       <c r="O33" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="B34" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="C34" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="D34" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="E34" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="F34" t="s">
-        <v>253</v>
+        <v>424</v>
       </c>
       <c r="G34" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="H34" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="I34" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="J34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K34" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="L34" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="M34" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="N34" t="s">
         <v>29</v>
       </c>
       <c r="O34" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="B35" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="C35" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="D35" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="E35" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="F35" t="s">
-        <v>117</v>
+        <v>435</v>
       </c>
       <c r="G35" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="H35" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="I35" t="s">
-        <v>426</v>
+        <v>156</v>
       </c>
       <c r="J35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K35" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="L35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M35" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="N35" t="s">
         <v>29</v>
       </c>
       <c r="O35" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="B36" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="C36" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D36" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="E36" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="F36" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="G36" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="H36" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="I36" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="J36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K36" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="L36" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="M36" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="N36" t="s">
         <v>29</v>
       </c>
       <c r="O36" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="B37" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="C37" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D37" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="E37" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="F37" t="s">
         <v>444</v>
       </c>
       <c r="G37" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="H37" t="s">
-        <v>436</v>
+        <v>453</v>
       </c>
       <c r="I37" t="s">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="J37" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="K37" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="L37" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="M37" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="N37" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="O37" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="B38" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="C38" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="D38" t="s">
-        <v>450</v>
+        <v>426</v>
       </c>
       <c r="E38" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F38" t="s">
         <v>452</v>
       </c>
       <c r="G38" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H38" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="I38" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="J38" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="K38" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="L38" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M38" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="N38" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="O38" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="B39" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C39" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="D39" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="E39" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F39" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="G39" t="s">
         <v>461</v>
       </c>
       <c r="H39" t="s">
-        <v>436</v>
+        <v>136</v>
       </c>
       <c r="I39" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="J39" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="K39" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="L39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M39" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="N39" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="O39" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="B40" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="C40" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="D40" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="E40" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="F40" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="G40" t="s">
-        <v>473</v>
+        <v>168</v>
       </c>
       <c r="H40" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="I40" t="s">
-        <v>164</v>
+        <v>233</v>
       </c>
       <c r="J40" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="K40" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="L40" t="s">
         <v>41</v>
       </c>
       <c r="M40" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="N40" t="s">
-        <v>478</v>
+        <v>209</v>
       </c>
       <c r="O40" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B41" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C41" t="s">
-        <v>167</v>
+        <v>487</v>
       </c>
       <c r="D41" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="E41" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="F41" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="G41" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="H41" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="I41" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="J41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K41" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L41" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M41" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="N41" t="s">
         <v>29</v>
       </c>
       <c r="O41" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="B42" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="C42" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="D42" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="E42" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="F42" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="G42" t="s">
-        <v>495</v>
+        <v>185</v>
       </c>
       <c r="H42" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="I42" t="s">
-        <v>183</v>
+        <v>503</v>
       </c>
       <c r="J42" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="K42" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="L42" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="M42" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="N42" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="O42" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="B43" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="C43" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D43" t="s">
-        <v>450</v>
+        <v>426</v>
       </c>
       <c r="E43" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="F43" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="G43" t="s">
-        <v>508</v>
+        <v>187</v>
       </c>
       <c r="H43" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="I43" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="J43" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K43" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="L43" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="M43" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="N43" t="s">
         <v>29</v>
       </c>
       <c r="O43" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="B44" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="C44" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D44" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E44" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F44" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="G44" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="H44" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="I44" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="J44" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K44" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="L44" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="M44" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="N44" t="s">
         <v>29</v>
       </c>
       <c r="O44" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="B45" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="C45" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="D45" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="E45" t="s">
-        <v>527</v>
+        <v>198</v>
       </c>
       <c r="F45" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="G45" t="s">
-        <v>529</v>
+        <v>216</v>
       </c>
       <c r="H45" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="I45" t="s">
-        <v>211</v>
+        <v>535</v>
       </c>
       <c r="J45" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K45" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="L45" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M45" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="N45" t="s">
         <v>29</v>
       </c>
       <c r="O45" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="B46" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C46" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="D46" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="E46" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F46" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="G46" t="s">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="H46" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="I46" t="s">
-        <v>179</v>
+        <v>545</v>
       </c>
       <c r="J46" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="K46" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="L46" t="s">
         <v>41</v>
       </c>
       <c r="M46" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="N46" t="s">
         <v>43</v>
       </c>
       <c r="O46" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B47" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C47" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="D47" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E47" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="F47" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="G47" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="H47" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="I47" t="s">
-        <v>549</v>
+        <v>513</v>
       </c>
       <c r="J47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K47" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="L47" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M47" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="N47" t="s">
         <v>29</v>
       </c>
       <c r="O47" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="B48" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="C48" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="D48" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="E48" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="F48" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="G48" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="H48" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="I48" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="J48" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K48" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="L48" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="M48" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="N48" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="O48" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="B49" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C49" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="D49" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="E49" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="F49" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="G49" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="H49" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="I49" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="J49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K49" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="L49" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="M49" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="N49" t="s">
         <v>29</v>
       </c>
       <c r="O49" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="B50" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="C50" t="s">
-        <v>581</v>
+        <v>148</v>
       </c>
       <c r="D50" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="E50" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="F50" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="G50" t="s">
-        <v>547</v>
+        <v>587</v>
       </c>
       <c r="H50" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="I50" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="J50" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K50" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="L50" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="M50" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="N50" t="s">
         <v>29</v>
       </c>
       <c r="O50" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="B51" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="C51" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="D51" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="E51" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="F51" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="G51" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="H51" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="I51" t="s">
-        <v>597</v>
+        <v>580</v>
       </c>
       <c r="J51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K51" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="L51" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M51" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="N51" t="s">
         <v>29</v>
       </c>
       <c r="O51" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B52" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C52" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D52" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E52" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="F52" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="G52" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="H52" t="s">
-        <v>604</v>
+        <v>444</v>
       </c>
       <c r="I52" t="s">
-        <v>417</v>
+        <v>608</v>
       </c>
       <c r="J52" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="K52" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="L52" t="s">
         <v>41</v>
       </c>
       <c r="M52" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="N52" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="O52" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B53" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C53" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D53" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="E53" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="F53" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="G53" t="s">
-        <v>611</v>
+        <v>466</v>
       </c>
       <c r="H53" t="s">
-        <v>612</v>
+        <v>426</v>
       </c>
       <c r="I53" t="s">
-        <v>453</v>
+        <v>615</v>
       </c>
       <c r="J53" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="K53" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="L53" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M53" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="N53" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="O53" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B54" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C54" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="D54" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="E54" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="F54" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="G54" t="s">
-        <v>623</v>
+        <v>117</v>
       </c>
       <c r="H54" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="I54" t="s">
-        <v>116</v>
+        <v>627</v>
       </c>
       <c r="J54" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="K54" t="s">
-        <v>180</v>
+        <v>629</v>
       </c>
       <c r="L54" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="M54" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="N54" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="O54" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B55" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="C55" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D55" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="E55" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="F55" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="G55" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="H55" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="I55" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="J55" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K55" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="L55" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="M55" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="N55" t="s">
         <v>29</v>
       </c>
       <c r="O55" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="B56" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C56" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="D56" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="E56" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="F56" t="s">
-        <v>122</v>
+        <v>645</v>
       </c>
       <c r="G56" t="s">
-        <v>641</v>
+        <v>436</v>
       </c>
       <c r="H56" t="s">
-        <v>642</v>
+        <v>232</v>
       </c>
       <c r="I56" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="J56" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K56" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="L56" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="M56" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="N56" t="s">
         <v>29</v>
       </c>
       <c r="O56" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B57" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C57" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D57" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="E57" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="F57" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="G57" t="s">
-        <v>116</v>
+        <v>615</v>
       </c>
       <c r="H57" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="I57" t="s">
-        <v>651</v>
+        <v>434</v>
       </c>
       <c r="J57" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K57" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="L57" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M57" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="N57" t="s">
         <v>29</v>
       </c>
       <c r="O57" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B58" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C58" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D58" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E58" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="F58" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="G58" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="H58" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="I58" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="J58" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="K58" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L58" t="s">
         <v>41</v>
       </c>
       <c r="M58" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="N58" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="O58" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B59" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C59" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D59" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="E59" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="F59" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="G59" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="H59" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="I59" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="J59" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="K59" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="L59" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M59" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="N59" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="O59" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B60" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C60" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D60" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E60" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="F60" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="G60" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="H60" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="I60" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="J60" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="K60" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="L60" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="M60" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="N60" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="O60" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B61" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C61" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D61" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E61" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="F61" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="G61" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="H61" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="I61" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="J61" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="K61" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="L61" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M61" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="N61" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="O61" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B62" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C62" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="D62" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E62" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="F62" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="G62" t="s">
         <v>716</v>
       </c>
       <c r="H62" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="I62" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="J62" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K62" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="L62" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="M62" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="N62" t="s">
         <v>29</v>
       </c>
       <c r="O62" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B63" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C63" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D63" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E63" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="F63" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="G63" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="H63" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="I63" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="J63" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K63" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="L63" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M63" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="N63" t="s">
         <v>29</v>
       </c>
       <c r="O63" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
     </row>
   </sheetData>

--- a/NUMEX_pre_RStudio/models_est.xlsx
+++ b/NUMEX_pre_RStudio/models_est.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="484">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -32,6 +32,9 @@
     <t xml:space="preserve">estimates.4</t>
   </si>
   <si>
+    <t xml:space="preserve">estimates.5</t>
+  </si>
+  <si>
     <t xml:space="preserve">gof</t>
   </si>
   <si>
@@ -56,6 +59,9 @@
     <t xml:space="preserve">P</t>
   </si>
   <si>
+    <t xml:space="preserve">N × P</t>
+  </si>
+  <si>
     <t xml:space="preserve">SD (Intercept Bloque)</t>
   </si>
   <si>
@@ -248,7 +254,7 @@
     <t xml:space="preserve">70.8</t>
   </si>
   <si>
-    <t xml:space="preserve">logNmass | 1000 | Pouteria</t>
+    <t xml:space="preserve">logLNC | 1000 | Pouteria</t>
   </si>
   <si>
     <t xml:space="preserve">2.74*** (SE = 0.03, p = &lt;0.01)</t>
@@ -275,7 +281,7 @@
     <t xml:space="preserve">-59.8</t>
   </si>
   <si>
-    <t xml:space="preserve">logNmass | 1000 | Clarisia</t>
+    <t xml:space="preserve">logLNC | 1000 | Clarisia</t>
   </si>
   <si>
     <t xml:space="preserve">2.84*** (SE = 0.06, p = &lt;0.01)</t>
@@ -296,7 +302,7 @@
     <t xml:space="preserve">1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">logNmass | 2000 | Alchornea</t>
+    <t xml:space="preserve">logLNC | 2000 | Alchornea</t>
   </si>
   <si>
     <t xml:space="preserve">2.45*** (SE = 0.03, p = &lt;0.01)</t>
@@ -317,7 +323,7 @@
     <t xml:space="preserve">-31.5</t>
   </si>
   <si>
-    <t xml:space="preserve">logNmass | 2000 | Myrcia</t>
+    <t xml:space="preserve">logLNC | 2000 | Myrcia</t>
   </si>
   <si>
     <t xml:space="preserve">2.16*** (SE = 0.03, p = &lt;0.01)</t>
@@ -344,7 +350,7 @@
     <t xml:space="preserve">-57.4</t>
   </si>
   <si>
-    <t xml:space="preserve">logNmass | 3000 | Hedyosmum</t>
+    <t xml:space="preserve">logLNC | 3000 | Hedyosmum</t>
   </si>
   <si>
     <t xml:space="preserve">2.68*** (SE = 0.06, p = &lt;0.01)</t>
@@ -371,7 +377,7 @@
     <t xml:space="preserve">-8.6</t>
   </si>
   <si>
-    <t xml:space="preserve">logNmass | 3000 | Weinmannia</t>
+    <t xml:space="preserve">logLNC | 3000 | Weinmannia</t>
   </si>
   <si>
     <t xml:space="preserve">2.35*** (SE = 0.06, p = &lt;0.01)</t>
@@ -557,22 +563,22 @@
     <t xml:space="preserve">Cmass | 1000 | Clarisia</t>
   </si>
   <si>
-    <t xml:space="preserve">427.48*** (SE = 7.99, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32 (SE = 9.23, p = 0.89)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28 (SE = 9.65, p = 0.54)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.30 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1</t>
+    <t xml:space="preserve">421.37*** (SE = 7.88, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.77 (SE = 15.77, p = 0.15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.97 (SE = 10.43, p = 0.15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-33.62 (SE = 18.49, p = 0.12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.65 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.4</t>
   </si>
   <si>
     <t xml:space="preserve">Cmass | 2000 | Alchornea</t>
@@ -815,7 +821,7 @@
     <t xml:space="preserve">112.6</t>
   </si>
   <si>
-    <t xml:space="preserve">logLCCC | 1000 | Pouteria</t>
+    <t xml:space="preserve">logLCC | 1000 | Pouteria</t>
   </si>
   <si>
     <t xml:space="preserve">6.17*** (SE = 0.00, p = &lt;0.01)</t>
@@ -833,25 +839,28 @@
     <t xml:space="preserve">-164.3</t>
   </si>
   <si>
-    <t xml:space="preserve">logLCCC |1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06*** (SE = 0.02, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.00 (SE = 0.02, p = 0.89)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01 (SE = 0.02, p = 0.53)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-20.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLCCC  | 2000 | Alchornea</t>
+    <t xml:space="preserve">logLCC |1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04*** (SE = 0.02, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.06 (SE = 0.04, p = 0.16)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04 (SE = 0.02, p = 0.16)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.08 (SE = 0.04, p = 0.12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-16.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLCC  | 2000 | Alchornea</t>
   </si>
   <si>
     <t xml:space="preserve">6.19*** (SE = 0.00, p = &lt;0.01)</t>
@@ -872,7 +881,7 @@
     <t xml:space="preserve">-191.4</t>
   </si>
   <si>
-    <t xml:space="preserve">logLCCC  | 2000 | Myrcia</t>
+    <t xml:space="preserve">logLCC  | 2000 | Myrcia</t>
   </si>
   <si>
     <t xml:space="preserve">6.16*** (SE = 0.00, p = &lt;0.01)</t>
@@ -890,7 +899,7 @@
     <t xml:space="preserve">-228.5</t>
   </si>
   <si>
-    <t xml:space="preserve">logLCCC  | 3000 | Hedyosmum</t>
+    <t xml:space="preserve">logLCC  | 3000 | Hedyosmum</t>
   </si>
   <si>
     <t xml:space="preserve">6.08*** (SE = 0.01, p = &lt;0.01)</t>
@@ -908,7 +917,7 @@
     <t xml:space="preserve">-78.0</t>
   </si>
   <si>
-    <t xml:space="preserve">logLCCC  | 3000 | Weinmannia</t>
+    <t xml:space="preserve">logLCC  | 3000 | Weinmannia</t>
   </si>
   <si>
     <t xml:space="preserve">6.09*** (SE = 0.01, p = &lt;0.01)</t>
@@ -998,19 +1007,25 @@
     <t xml:space="preserve">LPC | 2000 | Myrcia</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60*** (SE = 0.10, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.42** (SE = 0.12, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89*** (SE = 0.12, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6</t>
+    <t xml:space="preserve">0.43*** (SE = 0.10, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01 (SE = 0.16, p = 0.96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26*** (SE = 0.15, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.81*** (SE = 0.22, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6</t>
   </si>
   <si>
     <t xml:space="preserve">LPC | 3000 | Hedyosmum</t>
@@ -1040,103 +1055,106 @@
     <t xml:space="preserve">LPC | 3000 | Weinmannia</t>
   </si>
   <si>
-    <t xml:space="preserve">0.74*** (SE = 0.14, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.31+ (SE = 0.18, p = 0.10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75*** (SE = 0.17, p = &lt;0.01)</t>
+    <t xml:space="preserve">0.56*** (SE = 0.12, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.05 (SE = 0.17, p = 0.79)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08*** (SE = 0.16, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.96** (SE = 0.27, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.44*** (SE = 0.07, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.05 (SE = 0.07, p = 0.48)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17* (SE = 0.06, p = 0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.19* (SE = 0.06, p = 0.02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04 (SE = 0.07, p = 0.59)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32** (SE = 0.08, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.27*** (SE = 0.07, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.02 (SE = 0.07, p = 0.77)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46*** (SE = 0.06, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.21 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.88*** (SE = 0.09, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03 (SE = 0.14, p = 0.85)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32*** (SE = 0.14, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.66** (SE = 0.20, p = &lt;0.01)</t>
   </si>
   <si>
     <t xml:space="preserve">0.35 (SE = , p = )</t>
   </si>
   <si>
-    <t xml:space="preserve">0.619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.44*** (SE = 0.07, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.05 (SE = 0.07, p = 0.48)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17* (SE = 0.06, p = 0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.19* (SE = 0.06, p = 0.02)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.04 (SE = 0.07, p = 0.59)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32** (SE = 0.08, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.27*** (SE = 0.07, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.02 (SE = 0.07, p = 0.77)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46*** (SE = 0.06, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.21 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.75*** (SE = 0.09, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.31** (SE = 0.11, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01*** (SE = 0.11, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.3</t>
+    <t xml:space="preserve">0.707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8</t>
   </si>
   <si>
     <t xml:space="preserve">logLPC | 3000 | Hedyosmum</t>
@@ -1160,16 +1178,22 @@
     <t xml:space="preserve">logLPC | 3000 | Weinmannia</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.25 (SE = 0.14, p = 0.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8</t>
+    <t xml:space="preserve">-0.59*** (SE = 0.09, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08 (SE = 0.12, p = 0.52)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04*** (SE = 0.12, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.87*** (SE = 0.20, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4</t>
   </si>
   <si>
     <t xml:space="preserve">Parea | 1000 | Pouteria</t>
@@ -1373,28 +1397,31 @@
     <t xml:space="preserve">Leaf N:P | 2000 | Myrcia</t>
   </si>
   <si>
-    <t xml:space="preserve">21.71*** (SE = 1.11, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37** (SE = 1.16, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-14.15*** (SE = 1.18, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">279.4</t>
+    <t xml:space="preserve">22.85*** (SE = 1.14, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.67 (SE = 1.59, p = 0.67)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-16.58*** (SE = 1.52, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28* (SE = 2.23, p = 0.02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">272.6</t>
   </si>
   <si>
     <t xml:space="preserve">Leaf N:P | 3000 | Hedyosmum</t>
@@ -1421,22 +1448,22 @@
     <t xml:space="preserve">Leaf N:P | 3000 | Weinmannia</t>
   </si>
   <si>
-    <t xml:space="preserve">17.15*** (SE = 1.27, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25+ (SE = 1.57, p = 0.06)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.58*** (SE = 1.54, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7</t>
+    <t xml:space="preserve">18.65*** (SE = 1.12, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.23 (SE = 1.58, p = 0.88)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-11.34*** (SE = 1.51, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03** (SE = 2.58, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1</t>
   </si>
 </sst>
 </file>
@@ -1484,19 +1511,20 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:J63" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:J63"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K63" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K63"/>
+  <tableColumns count="11">
     <tableColumn id="1" name="Modelo"/>
     <tableColumn id="2" name="estimates"/>
     <tableColumn id="3" name="estimates.1"/>
     <tableColumn id="4" name="estimates.2"/>
     <tableColumn id="5" name="estimates.3"/>
     <tableColumn id="6" name="estimates.4"/>
-    <tableColumn id="7" name="gof"/>
-    <tableColumn id="8" name="gof.1"/>
-    <tableColumn id="9" name="gof.2"/>
-    <tableColumn id="10" name="gof.3"/>
+    <tableColumn id="7" name="estimates.5"/>
+    <tableColumn id="8" name="gof"/>
+    <tableColumn id="9" name="gof.1"/>
+    <tableColumn id="10" name="gof.2"/>
+    <tableColumn id="11" name="gof.3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1815,1989 +1843,2178 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="K4" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I5" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J5" t="s">
-        <v>41</v>
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I6" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="J6" t="s">
-        <v>49</v>
+        <v>24</v>
+      </c>
+      <c r="K6" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J7" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="K7" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J8" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="K8" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I9" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="J9" t="s">
-        <v>77</v>
+        <v>24</v>
+      </c>
+      <c r="K9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="H10" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="I10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J10" t="s">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="K10" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="H11" t="s">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="I11" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="J11" t="s">
-        <v>93</v>
+        <v>24</v>
+      </c>
+      <c r="K11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="H12" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="I12" t="s">
-        <v>22</v>
+        <v>101</v>
       </c>
       <c r="J12" t="s">
-        <v>100</v>
+        <v>24</v>
+      </c>
+      <c r="K12" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E13" t="s">
-        <v>105</v>
+        <v>24</v>
       </c>
       <c r="F13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G13" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="H13" t="s">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="I13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J13" t="s">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="K13" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="F14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G14" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="H14" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="I14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J14" t="s">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="K14" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F15" t="s">
-        <v>123</v>
+        <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="H15" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="I15" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="J15" t="s">
-        <v>125</v>
+        <v>24</v>
+      </c>
+      <c r="K15" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D16" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s">
-        <v>130</v>
+        <v>39</v>
       </c>
       <c r="G16" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="H16" t="s">
-        <v>131</v>
+        <v>31</v>
       </c>
       <c r="I16" t="s">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="J16" t="s">
-        <v>132</v>
+        <v>24</v>
+      </c>
+      <c r="K16" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B17" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C17" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D17" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s">
-        <v>137</v>
+        <v>39</v>
       </c>
       <c r="G17" t="s">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="H17" t="s">
-        <v>138</v>
+        <v>41</v>
       </c>
       <c r="I17" t="s">
-        <v>22</v>
+        <v>140</v>
       </c>
       <c r="J17" t="s">
-        <v>139</v>
+        <v>24</v>
+      </c>
+      <c r="K17" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B18" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C18" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D18" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E18" t="s">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="F18" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="G18" t="s">
-        <v>47</v>
+        <v>146</v>
       </c>
       <c r="H18" t="s">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="I18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J18" t="s">
-        <v>147</v>
+        <v>148</v>
+      </c>
+      <c r="K18" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B19" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C19" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D19" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E19" t="s">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="F19" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="G19" t="s">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="H19" t="s">
-        <v>153</v>
+        <v>58</v>
       </c>
       <c r="I19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J19" t="s">
-        <v>155</v>
+        <v>156</v>
+      </c>
+      <c r="K19" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B20" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C20" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D20" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E20" t="s">
-        <v>160</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G20" t="s">
-        <v>66</v>
+        <v>163</v>
       </c>
       <c r="H20" t="s">
-        <v>162</v>
+        <v>68</v>
       </c>
       <c r="I20" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J20" t="s">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="K20" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B21" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C21" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D21" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E21" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F21" t="s">
-        <v>169</v>
+        <v>39</v>
       </c>
       <c r="G21" t="s">
-        <v>75</v>
+        <v>171</v>
       </c>
       <c r="H21" t="s">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="I21" t="s">
-        <v>22</v>
+        <v>172</v>
       </c>
       <c r="J21" t="s">
-        <v>171</v>
+        <v>24</v>
+      </c>
+      <c r="K21" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B22" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D22" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E22" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F22" t="s">
-        <v>176</v>
+        <v>39</v>
       </c>
       <c r="G22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I22" t="s">
-        <v>22</v>
+        <v>180</v>
       </c>
       <c r="J22" t="s">
-        <v>179</v>
+        <v>24</v>
+      </c>
+      <c r="K22" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B23" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C23" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D23" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E23" t="s">
-        <v>37</v>
+        <v>186</v>
       </c>
       <c r="F23" t="s">
-        <v>184</v>
+        <v>39</v>
       </c>
       <c r="G23" t="s">
-        <v>39</v>
+        <v>187</v>
       </c>
       <c r="H23" t="s">
-        <v>185</v>
+        <v>41</v>
       </c>
       <c r="I23" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J23" t="s">
-        <v>186</v>
+        <v>24</v>
+      </c>
+      <c r="K23" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C24" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D24" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F24" t="s">
-        <v>191</v>
+        <v>39</v>
       </c>
       <c r="G24" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H24" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I24" t="s">
-        <v>22</v>
+        <v>195</v>
       </c>
       <c r="J24" t="s">
-        <v>194</v>
+        <v>24</v>
+      </c>
+      <c r="K24" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B25" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C25" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D25" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E25" t="s">
-        <v>199</v>
+        <v>24</v>
       </c>
       <c r="F25" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H25" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J25" t="s">
-        <v>204</v>
+        <v>205</v>
+      </c>
+      <c r="K25" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B26" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C26" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D26" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E26" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s">
-        <v>209</v>
+        <v>66</v>
       </c>
       <c r="G26" t="s">
-        <v>66</v>
+        <v>211</v>
       </c>
       <c r="H26" t="s">
-        <v>210</v>
+        <v>68</v>
       </c>
       <c r="I26" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J26" t="s">
-        <v>212</v>
+        <v>213</v>
+      </c>
+      <c r="K26" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B27" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C27" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D27" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E27" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>220</v>
       </c>
       <c r="H27" t="s">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="I27" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J27" t="s">
-        <v>221</v>
+        <v>222</v>
+      </c>
+      <c r="K27" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B28" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C28" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D28" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E28" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s">
-        <v>226</v>
+        <v>39</v>
       </c>
       <c r="G28" t="s">
-        <v>177</v>
+        <v>228</v>
       </c>
       <c r="H28" t="s">
-        <v>227</v>
+        <v>179</v>
       </c>
       <c r="I28" t="s">
-        <v>22</v>
+        <v>229</v>
       </c>
       <c r="J28" t="s">
-        <v>228</v>
+        <v>24</v>
+      </c>
+      <c r="K28" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B29" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C29" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D29" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E29" t="s">
-        <v>233</v>
+        <v>24</v>
       </c>
       <c r="F29" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G29" t="s">
-        <v>39</v>
+        <v>236</v>
       </c>
       <c r="H29" t="s">
-        <v>235</v>
+        <v>41</v>
       </c>
       <c r="I29" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J29" t="s">
-        <v>237</v>
+        <v>238</v>
+      </c>
+      <c r="K29" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B30" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C30" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D30" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>242</v>
+        <v>24</v>
       </c>
       <c r="F30" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G30" t="s">
-        <v>192</v>
+        <v>245</v>
       </c>
       <c r="H30" t="s">
-        <v>244</v>
+        <v>194</v>
       </c>
       <c r="I30" t="s">
-        <v>170</v>
+        <v>246</v>
       </c>
       <c r="J30" t="s">
-        <v>245</v>
+        <v>172</v>
+      </c>
+      <c r="K30" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B31" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C31" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D31" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E31" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F31" t="s">
-        <v>250</v>
+        <v>39</v>
       </c>
       <c r="G31" t="s">
-        <v>201</v>
+        <v>252</v>
       </c>
       <c r="H31" t="s">
-        <v>251</v>
+        <v>203</v>
       </c>
       <c r="I31" t="s">
-        <v>22</v>
+        <v>253</v>
       </c>
       <c r="J31" t="s">
-        <v>252</v>
+        <v>24</v>
+      </c>
+      <c r="K31" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B32" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C32" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D32" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E32" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F32" t="s">
-        <v>257</v>
+        <v>39</v>
       </c>
       <c r="G32" t="s">
-        <v>66</v>
+        <v>259</v>
       </c>
       <c r="H32" t="s">
-        <v>258</v>
+        <v>68</v>
       </c>
       <c r="I32" t="s">
-        <v>22</v>
+        <v>260</v>
       </c>
       <c r="J32" t="s">
-        <v>259</v>
+        <v>24</v>
+      </c>
+      <c r="K32" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B33" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C33" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D33" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E33" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F33" t="s">
-        <v>264</v>
+        <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>75</v>
+        <v>266</v>
       </c>
       <c r="H33" t="s">
-        <v>265</v>
+        <v>77</v>
       </c>
       <c r="I33" t="s">
-        <v>22</v>
+        <v>267</v>
       </c>
       <c r="J33" t="s">
-        <v>266</v>
+        <v>24</v>
+      </c>
+      <c r="K33" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B34" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C34" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D34" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E34" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F34" t="s">
-        <v>271</v>
+        <v>39</v>
       </c>
       <c r="G34" t="s">
-        <v>177</v>
+        <v>273</v>
       </c>
       <c r="H34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I34" t="s">
-        <v>22</v>
+        <v>180</v>
       </c>
       <c r="J34" t="s">
-        <v>272</v>
+        <v>24</v>
+      </c>
+      <c r="K34" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B35" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C35" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D35" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E35" t="s">
-        <v>37</v>
+        <v>279</v>
       </c>
       <c r="F35" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="G35" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="H35" t="s">
-        <v>277</v>
+        <v>41</v>
       </c>
       <c r="I35" t="s">
-        <v>22</v>
+        <v>280</v>
       </c>
       <c r="J35" t="s">
-        <v>278</v>
+        <v>24</v>
+      </c>
+      <c r="K35" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C36" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D36" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E36" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F36" t="s">
-        <v>283</v>
+        <v>39</v>
       </c>
       <c r="G36" t="s">
-        <v>192</v>
+        <v>286</v>
       </c>
       <c r="H36" t="s">
-        <v>284</v>
+        <v>194</v>
       </c>
       <c r="I36" t="s">
-        <v>22</v>
+        <v>287</v>
       </c>
       <c r="J36" t="s">
-        <v>285</v>
+        <v>24</v>
+      </c>
+      <c r="K36" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>289</v>
+      </c>
+      <c r="B37" t="s">
+        <v>290</v>
+      </c>
+      <c r="C37" t="s">
+        <v>291</v>
+      </c>
+      <c r="D37" t="s">
+        <v>292</v>
+      </c>
+      <c r="E37" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" t="s">
+        <v>39</v>
+      </c>
+      <c r="G37" t="s">
         <v>286</v>
       </c>
-      <c r="B37" t="s">
-        <v>287</v>
-      </c>
-      <c r="C37" t="s">
-        <v>288</v>
-      </c>
-      <c r="D37" t="s">
-        <v>289</v>
-      </c>
-      <c r="E37" t="s">
-        <v>37</v>
-      </c>
-      <c r="F37" t="s">
-        <v>283</v>
-      </c>
-      <c r="G37" t="s">
-        <v>201</v>
-      </c>
       <c r="H37" t="s">
-        <v>290</v>
+        <v>203</v>
       </c>
       <c r="I37" t="s">
-        <v>203</v>
+        <v>293</v>
       </c>
       <c r="J37" t="s">
-        <v>291</v>
+        <v>205</v>
+      </c>
+      <c r="K37" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B38" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C38" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D38" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E38" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F38" t="s">
-        <v>283</v>
+        <v>39</v>
       </c>
       <c r="G38" t="s">
-        <v>66</v>
+        <v>286</v>
       </c>
       <c r="H38" t="s">
-        <v>296</v>
+        <v>68</v>
       </c>
       <c r="I38" t="s">
-        <v>22</v>
+        <v>299</v>
       </c>
       <c r="J38" t="s">
-        <v>297</v>
+        <v>24</v>
+      </c>
+      <c r="K38" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B39" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C39" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E39" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F39" t="s">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="G39" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="H39" t="s">
-        <v>302</v>
+        <v>77</v>
       </c>
       <c r="I39" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J39" t="s">
-        <v>304</v>
+        <v>306</v>
+      </c>
+      <c r="K39" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B40" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C40" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E40" t="s">
-        <v>309</v>
+        <v>24</v>
       </c>
       <c r="F40" t="s">
-        <v>98</v>
+        <v>312</v>
       </c>
       <c r="G40" t="s">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="H40" t="s">
-        <v>310</v>
+        <v>31</v>
       </c>
       <c r="I40" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J40" t="s">
-        <v>312</v>
+        <v>314</v>
+      </c>
+      <c r="K40" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B41" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C41" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D41" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E41" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F41" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="G41" t="s">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="H41" t="s">
-        <v>317</v>
+        <v>41</v>
       </c>
       <c r="I41" t="s">
-        <v>22</v>
+        <v>320</v>
       </c>
       <c r="J41" t="s">
-        <v>318</v>
+        <v>24</v>
+      </c>
+      <c r="K41" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B42" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C42" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D42" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E42" t="s">
-        <v>160</v>
+        <v>24</v>
       </c>
       <c r="F42" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="G42" t="s">
-        <v>323</v>
+        <v>171</v>
       </c>
       <c r="H42" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I42" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J42" t="s">
-        <v>326</v>
+        <v>328</v>
+      </c>
+      <c r="K42" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B43" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C43" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D43" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E43" t="s">
-        <v>37</v>
+        <v>334</v>
       </c>
       <c r="F43" t="s">
-        <v>331</v>
+        <v>39</v>
       </c>
       <c r="G43" t="s">
-        <v>201</v>
+        <v>335</v>
       </c>
       <c r="H43" t="s">
-        <v>92</v>
+        <v>203</v>
       </c>
       <c r="I43" t="s">
-        <v>22</v>
+        <v>336</v>
       </c>
       <c r="J43" t="s">
-        <v>332</v>
+        <v>24</v>
+      </c>
+      <c r="K43" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B44" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C44" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="D44" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="E44" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F44" t="s">
-        <v>337</v>
+        <v>39</v>
       </c>
       <c r="G44" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="H44" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="I44" t="s">
-        <v>22</v>
+        <v>344</v>
       </c>
       <c r="J44" t="s">
-        <v>340</v>
+        <v>24</v>
+      </c>
+      <c r="K44" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B45" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C45" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="D45" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E45" t="s">
-        <v>37</v>
+        <v>350</v>
       </c>
       <c r="F45" t="s">
-        <v>345</v>
+        <v>39</v>
       </c>
       <c r="G45" t="s">
-        <v>75</v>
+        <v>351</v>
       </c>
       <c r="H45" t="s">
-        <v>346</v>
+        <v>77</v>
       </c>
       <c r="I45" t="s">
-        <v>22</v>
+        <v>352</v>
       </c>
       <c r="J45" t="s">
-        <v>347</v>
+        <v>24</v>
+      </c>
+      <c r="K45" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B46" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C46" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="D46" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="E46" t="s">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="F46" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="G46" t="s">
-        <v>29</v>
+        <v>139</v>
       </c>
       <c r="H46" t="s">
-        <v>352</v>
+        <v>31</v>
       </c>
       <c r="I46" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="J46" t="s">
-        <v>354</v>
+        <v>358</v>
+      </c>
+      <c r="K46" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B47" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C47" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="D47" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="E47" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F47" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="G47" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s">
-        <v>359</v>
+        <v>41</v>
       </c>
       <c r="I47" t="s">
-        <v>22</v>
+        <v>364</v>
       </c>
       <c r="J47" t="s">
-        <v>360</v>
+        <v>24</v>
+      </c>
+      <c r="K47" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B48" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C48" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="D48" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="E48" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="F48" t="s">
-        <v>365</v>
+        <v>108</v>
       </c>
       <c r="G48" t="s">
-        <v>323</v>
+        <v>370</v>
       </c>
       <c r="H48" t="s">
-        <v>366</v>
+        <v>326</v>
       </c>
       <c r="I48" t="s">
-        <v>317</v>
+        <v>371</v>
       </c>
       <c r="J48" t="s">
-        <v>367</v>
+        <v>320</v>
+      </c>
+      <c r="K48" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B49" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C49" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="D49" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="E49" t="s">
-        <v>37</v>
+        <v>377</v>
       </c>
       <c r="F49" t="s">
-        <v>372</v>
+        <v>39</v>
       </c>
       <c r="G49" t="s">
-        <v>201</v>
+        <v>378</v>
       </c>
       <c r="H49" t="s">
-        <v>373</v>
+        <v>203</v>
       </c>
       <c r="I49" t="s">
-        <v>22</v>
+        <v>379</v>
       </c>
       <c r="J49" t="s">
-        <v>374</v>
+        <v>24</v>
+      </c>
+      <c r="K49" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B50" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C50" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="D50" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="E50" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F50" t="s">
-        <v>137</v>
+        <v>39</v>
       </c>
       <c r="G50" t="s">
-        <v>338</v>
+        <v>139</v>
       </c>
       <c r="H50" t="s">
-        <v>379</v>
+        <v>343</v>
       </c>
       <c r="I50" t="s">
-        <v>22</v>
+        <v>385</v>
       </c>
       <c r="J50" t="s">
-        <v>380</v>
+        <v>24</v>
+      </c>
+      <c r="K50" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B51" t="s">
-        <v>329</v>
+        <v>388</v>
       </c>
       <c r="C51" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="D51" t="s">
-        <v>342</v>
+        <v>390</v>
       </c>
       <c r="E51" t="s">
-        <v>37</v>
+        <v>391</v>
       </c>
       <c r="F51" t="s">
-        <v>383</v>
+        <v>39</v>
       </c>
       <c r="G51" t="s">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="H51" t="s">
-        <v>384</v>
+        <v>77</v>
       </c>
       <c r="I51" t="s">
-        <v>22</v>
+        <v>392</v>
       </c>
       <c r="J51" t="s">
-        <v>385</v>
+        <v>24</v>
+      </c>
+      <c r="K51" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B52" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C52" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D52" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="E52" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F52" t="s">
-        <v>271</v>
+        <v>39</v>
       </c>
       <c r="G52" t="s">
-        <v>29</v>
+        <v>273</v>
       </c>
       <c r="H52" t="s">
-        <v>390</v>
+        <v>31</v>
       </c>
       <c r="I52" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="J52" t="s">
-        <v>392</v>
+        <v>399</v>
+      </c>
+      <c r="K52" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="B53" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C53" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="D53" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="E53" t="s">
-        <v>271</v>
+        <v>24</v>
       </c>
       <c r="F53" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G53" t="s">
-        <v>39</v>
+        <v>273</v>
       </c>
       <c r="H53" t="s">
-        <v>397</v>
+        <v>41</v>
       </c>
       <c r="I53" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="J53" t="s">
-        <v>399</v>
+        <v>406</v>
+      </c>
+      <c r="K53" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="B54" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C54" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="D54" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="E54" t="s">
-        <v>271</v>
+        <v>24</v>
       </c>
       <c r="F54" t="s">
-        <v>114</v>
+        <v>273</v>
       </c>
       <c r="G54" t="s">
-        <v>323</v>
+        <v>116</v>
       </c>
       <c r="H54" t="s">
-        <v>404</v>
+        <v>326</v>
       </c>
       <c r="I54" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="J54" t="s">
-        <v>406</v>
+        <v>413</v>
+      </c>
+      <c r="K54" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B55" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C55" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="D55" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="E55" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F55" t="s">
-        <v>123</v>
+        <v>39</v>
       </c>
       <c r="G55" t="s">
-        <v>201</v>
+        <v>125</v>
       </c>
       <c r="H55" t="s">
-        <v>411</v>
+        <v>203</v>
       </c>
       <c r="I55" t="s">
-        <v>22</v>
+        <v>419</v>
       </c>
       <c r="J55" t="s">
-        <v>412</v>
+        <v>24</v>
+      </c>
+      <c r="K55" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B56" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C56" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="D56" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="E56" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F56" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="G56" t="s">
-        <v>338</v>
+        <v>84</v>
       </c>
       <c r="H56" t="s">
-        <v>417</v>
+        <v>343</v>
       </c>
       <c r="I56" t="s">
-        <v>22</v>
+        <v>425</v>
       </c>
       <c r="J56" t="s">
-        <v>418</v>
+        <v>24</v>
+      </c>
+      <c r="K56" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="B57" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C57" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D57" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="E57" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F57" t="s">
-        <v>309</v>
+        <v>39</v>
       </c>
       <c r="G57" t="s">
-        <v>75</v>
+        <v>312</v>
       </c>
       <c r="H57" t="s">
-        <v>423</v>
+        <v>77</v>
       </c>
       <c r="I57" t="s">
-        <v>22</v>
+        <v>431</v>
       </c>
       <c r="J57" t="s">
-        <v>424</v>
+        <v>24</v>
+      </c>
+      <c r="K57" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="B58" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="C58" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="D58" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="E58" t="s">
-        <v>429</v>
+        <v>24</v>
       </c>
       <c r="F58" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="G58" t="s">
-        <v>29</v>
+        <v>438</v>
       </c>
       <c r="H58" t="s">
-        <v>431</v>
+        <v>31</v>
       </c>
       <c r="I58" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="J58" t="s">
-        <v>433</v>
+        <v>440</v>
+      </c>
+      <c r="K58" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="B59" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C59" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="D59" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="E59" t="s">
-        <v>438</v>
+        <v>24</v>
       </c>
       <c r="F59" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="G59" t="s">
-        <v>39</v>
+        <v>447</v>
       </c>
       <c r="H59" t="s">
-        <v>440</v>
+        <v>41</v>
       </c>
       <c r="I59" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="J59" t="s">
-        <v>442</v>
+        <v>449</v>
+      </c>
+      <c r="K59" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="B60" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="C60" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="D60" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="E60" t="s">
-        <v>447</v>
+        <v>24</v>
       </c>
       <c r="F60" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="G60" t="s">
-        <v>323</v>
+        <v>456</v>
       </c>
       <c r="H60" t="s">
-        <v>449</v>
+        <v>326</v>
       </c>
       <c r="I60" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="J60" t="s">
-        <v>451</v>
+        <v>458</v>
+      </c>
+      <c r="K60" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B61" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C61" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="D61" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="E61" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="F61" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="G61" t="s">
-        <v>56</v>
+        <v>466</v>
       </c>
       <c r="H61" t="s">
-        <v>458</v>
+        <v>58</v>
       </c>
       <c r="I61" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="J61" t="s">
-        <v>460</v>
+        <v>468</v>
+      </c>
+      <c r="K61" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="B62" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="C62" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="D62" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="E62" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F62" t="s">
-        <v>465</v>
+        <v>39</v>
       </c>
       <c r="G62" t="s">
-        <v>338</v>
+        <v>474</v>
       </c>
       <c r="H62" t="s">
-        <v>466</v>
+        <v>343</v>
       </c>
       <c r="I62" t="s">
-        <v>22</v>
+        <v>475</v>
       </c>
       <c r="J62" t="s">
-        <v>467</v>
+        <v>24</v>
+      </c>
+      <c r="K62" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="B63" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="C63" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="D63" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="E63" t="s">
-        <v>37</v>
+        <v>481</v>
       </c>
       <c r="F63" t="s">
-        <v>472</v>
+        <v>39</v>
       </c>
       <c r="G63" t="s">
-        <v>75</v>
+        <v>236</v>
       </c>
       <c r="H63" t="s">
-        <v>473</v>
+        <v>77</v>
       </c>
       <c r="I63" t="s">
-        <v>22</v>
+        <v>482</v>
       </c>
       <c r="J63" t="s">
-        <v>474</v>
+        <v>24</v>
+      </c>
+      <c r="K63" t="s">
+        <v>483</v>
       </c>
     </row>
   </sheetData>

--- a/NUMEX_pre_RStudio/models_est.xlsx
+++ b/NUMEX_pre_RStudio/models_est.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="482">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -92,1221 +92,1221 @@
     <t xml:space="preserve">Nmass | 1000 | Pouteria</t>
   </si>
   <si>
-    <t xml:space="preserve">15.54*** (SE = 0.42, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.07 (SE = 0.42, p = 0.86)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92* (SE = 0.40, p = 0.03)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116</t>
+    <t xml:space="preserve">15.69*** (SE = 0.44, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.08 (SE = 0.45, p = 0.86)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.82+ (SE = 0.44, p = 0.07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nmass | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.14*** (SE = 1.13, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66* (SE = 1.31, p = 0.03)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66+ (SE = 1.37, p = 0.09)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nmass | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.73*** (SE = 0.41, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27* (SE = 0.49, p = 0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.78 (SE = 0.49, p = 0.12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nmass | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72*** (SE = 0.27, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41*** (SE = 0.27, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.42 (SE = 0.27, p = 0.13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nmass | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.54*** (SE = 0.98, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34* (SE = 0.92, p = 0.02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.63 (SE = 0.93, p = 0.51)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nmass | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.54*** (SE = 0.61, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81 (SE = 0.76, p = 0.30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09 (SE = 0.74, p = 0.90)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLNC | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75*** (SE = 0.03, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.00 (SE = 0.03, p = 0.86)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.05+ (SE = 0.03, p = 0.07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.07 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-48.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLNC | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84*** (SE = 0.06, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.18* (SE = 0.07, p = 0.04)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13 (SE = 0.07, p = 0.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLNC | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45*** (SE = 0.04, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11* (SE = 0.04, p = 0.02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.06 (SE = 0.04, p = 0.14)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-26.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLNC | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16*** (SE = 0.03, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16*** (SE = 0.03, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.05 (SE = 0.03, p = 0.13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-56.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLNC | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67*** (SE = 0.06, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14* (SE = 0.05, p = 0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.05 (SE = 0.05, p = 0.39)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLNC | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35*** (SE = 0.06, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08 (SE = 0.07, p = 0.29)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01 (SE = 0.07, p = 0.87)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narea | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99*** (SE = 0.08, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01 (SE = 0.10, p = 0.94)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12 (SE = 0.10, p = 0.22)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.02 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narea | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85*** (SE = 0.10, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.07 (SE = 0.12, p = 0.56)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.23+ (SE = 0.12, p = 0.09)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.19 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narea | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26*** (SE = 0.15, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35* (SE = 0.17, p = 0.05)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.12 (SE = 0.17, p = 0.50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narea | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45*** (SE = 0.07, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36*** (SE = 0.07, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.07 (SE = 0.07, p = 0.32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narea | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16*** (SE = 0.15, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59** (SE = 0.16, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.12 (SE = 0.16, p = 0.48)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narea | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51*** (SE = 0.09, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14 (SE = 0.11, p = 0.23)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.04 (SE = 0.11, p = 0.73)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.22 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmass | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">479.01*** (SE = 1.95, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.18 (SE = 2.24, p = 0.94)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.29 (SE = 2.24, p = 0.90)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmass | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.37*** (SE = 7.88, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.77 (SE = 15.77, p = 0.15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.97 (SE = 10.43, p = 0.15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-33.62 (SE = 18.49, p = 0.12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.65 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">0.265</t>
   </si>
   <si>
-    <t xml:space="preserve">124.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nmass | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.14*** (SE = 1.13, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66* (SE = 1.31, p = 0.03)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66+ (SE = 1.37, p = 0.09)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.00 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nmass | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.74*** (SE = 0.39, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24* (SE = 0.47, p = 0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.75 (SE = 0.46, p = 0.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nmass | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74*** (SE = 0.27, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36*** (SE = 0.27, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.47+ (SE = 0.27, p = 0.09)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92 (SE = , p = )</t>
+    <t xml:space="preserve">80.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmass | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">488.74*** (SE = 2.26, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39 (SE = 2.81, p = 0.89)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.62 (SE = 2.79, p = 0.82)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">283.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmass | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">473.21*** (SE = 2.20, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.19 (SE = 2.36, p = 0.18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.41+ (SE = 2.38, p = 0.07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">49</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nmass | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.64*** (SE = 1.02, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45* (SE = 0.91, p = 0.02)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52 (SE = 0.91, p = 0.58)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nmass | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.54*** (SE = 0.61, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81 (SE = 0.76, p = 0.30)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.09 (SE = 0.74, p = 0.90)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLNC | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74*** (SE = 0.03, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.00 (SE = 0.03, p = 0.87)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.06* (SE = 0.02, p = 0.03)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.04 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.07 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-59.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLNC | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84*** (SE = 0.06, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.18* (SE = 0.07, p = 0.04)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13 (SE = 0.07, p = 0.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLNC | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45*** (SE = 0.03, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10* (SE = 0.04, p = 0.02)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.06 (SE = 0.04, p = 0.14)</t>
+    <t xml:space="preserve">0.104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">344.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmass | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">435.97*** (SE = 3.01, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.22 (SE = 3.41, p = 0.95)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00 (SE = 3.45, p = 0.40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmass | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">440.61*** (SE = 4.84, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15 (SE = 5.82, p = 0.18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11 (SE = 5.73, p = 0.60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.60 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carea | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.35*** (SE = 2.92, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66 (SE = 3.34, p = 0.62)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.75 (SE = 3.34, p = 0.82)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carea | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.40*** (SE = 2.12, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.79* (SE = 1.57, p = 0.02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.37 (SE = 1.58, p = 0.82)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carea | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.05*** (SE = 5.08, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.16 (SE = 5.16, p = 0.98)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77 (SE = 5.17, p = 0.36)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.05 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carea | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.16*** (SE = 3.20, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.80 (SE = 4.00, p = 0.35)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31 (SE = 3.98, p = 0.74)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.85 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">391.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carea | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.41*** (SE = 4.25, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40 (SE = 4.91, p = 0.21)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.39 (SE = 4.95, p = 0.22)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.88 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carea | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.37*** (SE = 2.46, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01 (SE = 3.05, p = 0.52)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.25 (SE = 2.99, p = 0.47)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLCC | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17*** (SE = 0.00, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.00 (SE = 0.00, p = 0.94)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.00 (SE = 0.00, p = 0.90)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-136.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLCC |1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04*** (SE = 0.02, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.06 (SE = 0.04, p = 0.16)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04 (SE = 0.02, p = 0.16)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.08 (SE = 0.04, p = 0.12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-16.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLCC  | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19*** (SE = 0.00, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00 (SE = 0.01, p = 0.90)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.00 (SE = 0.01, p = 0.83)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-174.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLCC  | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16*** (SE = 0.00, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01 (SE = 0.00, p = 0.19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01+ (SE = 0.01, p = 0.07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-222.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLCC  | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08*** (SE = 0.01, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00 (SE = 0.01, p = 0.96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01 (SE = 0.01, p = 0.40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-78.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLCC  | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09*** (SE = 0.01, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.02 (SE = 0.01, p = 0.19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01 (SE = 0.01, p = 0.61)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-50.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.66*** (SE = 0.04, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00 (SE = 0.05, p = 0.93)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08 (SE = 0.05, p = 0.13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-11.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83*** (SE = 0.07, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03 (SE = 0.08, p = 0.72)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32** (SE = 0.09, p = &lt;0.01)</t>
   </si>
   <si>
     <t xml:space="preserve">0.13 (SE = , p = )</t>
   </si>
   <si>
-    <t xml:space="preserve">0.180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-31.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLNC | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16*** (SE = 0.03, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15*** (SE = 0.03, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.05+ (SE = 0.03, p = 0.09)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.03 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-57.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLNC | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68*** (SE = 0.06, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15* (SE = 0.05, p = 0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.04 (SE = 0.05, p = 0.45)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.08 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLNC | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35*** (SE = 0.06, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.08 (SE = 0.07, p = 0.29)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01 (SE = 0.07, p = 0.87)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narea | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96*** (SE = 0.07, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.03 (SE = 0.08, p = 0.68)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15+ (SE = 0.08, p = 0.10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.081</t>
+    <t xml:space="preserve">0.591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.76*** (SE = 0.07, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04 (SE = 0.07, p = 0.60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48*** (SE = 0.07, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.23 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.43*** (SE = 0.10, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01 (SE = 0.16, p = 0.96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26*** (SE = 0.15, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.79*** (SE = 0.22, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94*** (SE = 0.09, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.20+ (SE = 0.10, p = 0.06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50*** (SE = 0.10, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.21 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56*** (SE = 0.12, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.05 (SE = 0.17, p = 0.79)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08*** (SE = 0.16, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.96** (SE = 0.27, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.781</t>
   </si>
   <si>
     <t xml:space="preserve">20.4</t>
   </si>
   <si>
-    <t xml:space="preserve">Narea | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85*** (SE = 0.10, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.07 (SE = 0.12, p = 0.56)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23+ (SE = 0.12, p = 0.09)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.19 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narea | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26*** (SE = 0.14, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35* (SE = 0.16, p = 0.04)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.11 (SE = 0.16, p = 0.49)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narea | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45*** (SE = 0.07, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35*** (SE = 0.07, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.08 (SE = 0.07, p = 0.29)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narea | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19*** (SE = 0.15, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60** (SE = 0.16, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.12 (SE = 0.16, p = 0.49)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.09 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narea | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51*** (SE = 0.09, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14 (SE = 0.11, p = 0.23)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.04 (SE = 0.11, p = 0.73)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.22 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmass | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">478.86*** (SE = 1.64, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79 (SE = 1.95, p = 0.69)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.60 (SE = 1.95, p = 0.76)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmass | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.37*** (SE = 7.88, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.77 (SE = 15.77, p = 0.15)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.97 (SE = 10.43, p = 0.15)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-33.62 (SE = 18.49, p = 0.12)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.65 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmass | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">488.70*** (SE = 2.19, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46 (SE = 2.69, p = 0.86)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.72 (SE = 2.63, p = 0.79)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmass | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">473.23*** (SE = 2.18, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.23 (SE = 2.31, p = 0.17)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.46+ (SE = 2.33, p = 0.06)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmass | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">435.91*** (SE = 3.05, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.78 (SE = 3.46, p = 0.82)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37 (SE = 3.44, p = 0.50)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmass | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">440.61*** (SE = 4.84, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15 (SE = 5.82, p = 0.18)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11 (SE = 5.73, p = 0.60)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.60 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carea | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.42*** (SE = 2.45, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21 (SE = 2.91, p = 0.45)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.75 (SE = 2.93, p = 0.80)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">230.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carea | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.40*** (SE = 2.12, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.79* (SE = 1.57, p = 0.02)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.37 (SE = 1.58, p = 0.82)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carea | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.02*** (SE = 5.16, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.27 (SE = 5.37, p = 0.96)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81 (SE = 5.30, p = 0.37)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.07 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">361.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carea | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.96*** (SE = 3.18, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.30 (SE = 3.95, p = 0.41)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76 (SE = 3.94, p = 0.66)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.82 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carea | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.89*** (SE = 4.20, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84 (SE = 4.90, p = 0.18)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.50 (SE = 4.85, p = 0.20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.76 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carea | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.37*** (SE = 2.46, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01 (SE = 3.05, p = 0.52)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.25 (SE = 2.99, p = 0.47)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLCC | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17*** (SE = 0.00, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.00 (SE = 0.00, p = 0.69)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.00 (SE = 0.00, p = 0.76)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-164.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLCC |1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04*** (SE = 0.02, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.06 (SE = 0.04, p = 0.16)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.04 (SE = 0.02, p = 0.16)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.08 (SE = 0.04, p = 0.12)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-16.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLCC  | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19*** (SE = 0.00, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.00 (SE = 0.01, p = 0.88)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.00 (SE = 0.01, p = 0.80)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.02 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-191.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLCC  | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16*** (SE = 0.00, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.01 (SE = 0.00, p = 0.17)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.01+ (SE = 0.00, p = 0.06)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-228.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLCC  | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08*** (SE = 0.01, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.00 (SE = 0.01, p = 0.84)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01 (SE = 0.01, p = 0.50)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-78.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLCC  | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09*** (SE = 0.01, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.02 (SE = 0.01, p = 0.19)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01 (SE = 0.01, p = 0.61)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-50.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.66*** (SE = 0.05, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.03 (SE = 0.05, p = 0.57)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11* (SE = 0.05, p = 0.03)</t>
+    <t xml:space="preserve">logLPC | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.44*** (SE = 0.06, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00 (SE = 0.07, p = 0.98)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13+ (SE = 0.07, p = 0.08)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.19* (SE = 0.06, p = 0.02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04 (SE = 0.07, p = 0.59)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32** (SE = 0.08, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.28*** (SE = 0.07, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03 (SE = 0.07, p = 0.69)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45*** (SE = 0.07, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.88*** (SE = 0.09, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03 (SE = 0.14, p = 0.85)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32*** (SE = 0.14, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.63** (SE = 0.20, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.11 (SE = 0.06, p = 0.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.15* (SE = 0.06, p = 0.03)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.06 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logLPC | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.59*** (SE = 0.09, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08 (SE = 0.12, p = 0.52)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04*** (SE = 0.12, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.87*** (SE = 0.20, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parea | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08*** (SE = 0.00, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00 (SE = 0.00, p = 0.90)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01* (SE = 0.00, p = 0.02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-148.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parea | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09*** (SE = 0.01, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01 (SE = 0.01, p = 0.37)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03** (SE = 0.01, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.630</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-35.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parea | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.21*** (SE = 0.02, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01 (SE = 0.02, p = 0.57)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15*** (SE = 0.02, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-67.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parea | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17*** (SE = 0.03, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.13** (SE = 0.04, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27*** (SE = 0.04, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-30.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parea | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14*** (SE = 0.01, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01 (SE = 0.02, p = 0.52)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.06** (SE = 0.02, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-48.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parea | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10*** (SE = 0.02, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.04 (SE = 0.02, p = 0.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10** (SE = 0.02, p = &lt;0.01)</t>
   </si>
   <si>
     <t xml:space="preserve">0.05 (SE = , p = )</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-19.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83*** (SE = 0.07, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.03 (SE = 0.08, p = 0.72)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32** (SE = 0.09, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76*** (SE = 0.07, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.03 (SE = 0.07, p = 0.66)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49*** (SE = 0.07, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.590</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43*** (SE = 0.10, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.01 (SE = 0.16, p = 0.96)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26*** (SE = 0.15, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.81*** (SE = 0.22, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.91*** (SE = 0.10, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.17 (SE = 0.12, p = 0.18)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45** (SE = 0.12, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56*** (SE = 0.12, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.05 (SE = 0.17, p = 0.79)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08*** (SE = 0.16, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.96** (SE = 0.27, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.44*** (SE = 0.07, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.05 (SE = 0.07, p = 0.48)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17* (SE = 0.06, p = 0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.19* (SE = 0.06, p = 0.02)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.04 (SE = 0.07, p = 0.59)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32** (SE = 0.08, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.27*** (SE = 0.07, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.02 (SE = 0.07, p = 0.77)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46*** (SE = 0.06, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.21 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.88*** (SE = 0.09, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.03 (SE = 0.14, p = 0.85)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32*** (SE = 0.14, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.66** (SE = 0.20, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.14+ (SE = 0.07, p = 0.08)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.13 (SE = 0.09, p = 0.16)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41*** (SE = 0.09, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logLPC | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.59*** (SE = 0.09, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.08 (SE = 0.12, p = 0.52)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04*** (SE = 0.12, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.87*** (SE = 0.20, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parea | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.08*** (SE = 0.00, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.00 (SE = 0.00, p = 0.42)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.02*** (SE = 0.00, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-179.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parea | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.09*** (SE = 0.01, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.01 (SE = 0.01, p = 0.37)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.03** (SE = 0.01, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.630</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-35.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parea | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.21*** (SE = 0.02, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01 (SE = 0.02, p = 0.59)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15*** (SE = 0.02, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-75.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parea | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17*** (SE = 0.03, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.13** (SE = 0.04, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26*** (SE = 0.04, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-31.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parea | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13*** (SE = 0.02, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.01 (SE = 0.02, p = 0.72)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.05* (SE = 0.02, p = 0.02)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-45.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parea | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10*** (SE = 0.02, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.04 (SE = 0.02, p = 0.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10** (SE = 0.02, p = &lt;0.01)</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.603</t>
   </si>
   <si>
@@ -1316,28 +1316,19 @@
     <t xml:space="preserve">Leaf N:P | 1000 | Pouteria</t>
   </si>
   <si>
-    <t xml:space="preserve">24.75*** (SE = 1.41, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88 (SE = 1.61, p = 0.59)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.75+ (SE = 1.58, p = 0.09)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.9</t>
+    <t xml:space="preserve">25.02*** (SE = 1.47, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.29 (SE = 1.77, p = 0.87)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.20 (SE = 1.78, p = 0.23)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.1</t>
   </si>
   <si>
     <t xml:space="preserve">Leaf N:P | 1000 | Clarisia</t>
@@ -1370,79 +1361,82 @@
     <t xml:space="preserve">Leaf N:P | 2000 | Alchornea</t>
   </si>
   <si>
-    <t xml:space="preserve">15.43*** (SE = 0.80, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22+ (SE = 0.62, p = 0.05)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.33*** (SE = 0.61, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">195.9</t>
+    <t xml:space="preserve">15.44*** (SE = 0.81, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18+ (SE = 0.66, p = 0.08)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.30*** (SE = 0.65, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.8</t>
   </si>
   <si>
     <t xml:space="preserve">Leaf N:P | 2000 | Myrcia</t>
   </si>
   <si>
-    <t xml:space="preserve">22.85*** (SE = 1.14, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.67 (SE = 1.59, p = 0.67)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-16.58*** (SE = 1.52, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28* (SE = 2.23, p = 0.02)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85 (SE = , p = )</t>
+    <t xml:space="preserve">22.85*** (SE = 1.15, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.67 (SE = 1.61, p = 0.68)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-16.58*** (SE = 1.54, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22* (SE = 2.28, p = 0.03)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">0.771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">272.6</t>
+    <t xml:space="preserve">0.783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">267.9</t>
   </si>
   <si>
     <t xml:space="preserve">Leaf N:P | 3000 | Hedyosmum</t>
   </si>
   <si>
-    <t xml:space="preserve">17.36*** (SE = 1.22, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26** (SE = 1.43, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.37** (SE = 1.43, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.0</t>
+    <t xml:space="preserve">16.76*** (SE = 1.06, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61*** (SE = 1.11, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.98*** (SE = 1.14, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9</t>
   </si>
   <si>
     <t xml:space="preserve">Leaf N:P | 3000 | Weinmannia</t>
@@ -2153,27 +2147,27 @@
         <v>31</v>
       </c>
       <c r="I10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" t="s">
         <v>86</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>87</v>
-      </c>
-      <c r="K10" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" t="s">
         <v>89</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>90</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>91</v>
-      </c>
-      <c r="D11" t="s">
-        <v>92</v>
       </c>
       <c r="E11" t="s">
         <v>24</v>
@@ -2182,33 +2176,33 @@
         <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H11" t="s">
         <v>41</v>
       </c>
       <c r="I11" t="s">
+        <v>93</v>
+      </c>
+      <c r="J11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" t="s">
         <v>94</v>
-      </c>
-      <c r="J11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K11" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" t="s">
         <v>96</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>97</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>98</v>
-      </c>
-      <c r="D12" t="s">
-        <v>99</v>
       </c>
       <c r="E12" t="s">
         <v>24</v>
@@ -2217,103 +2211,103 @@
         <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H12" t="s">
         <v>49</v>
       </c>
       <c r="I12" t="s">
+        <v>100</v>
+      </c>
+      <c r="J12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" t="s">
         <v>101</v>
-      </c>
-      <c r="J12" t="s">
-        <v>24</v>
-      </c>
-      <c r="K12" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" t="s">
         <v>103</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>104</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>105</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" t="s">
         <v>106</v>
       </c>
-      <c r="E13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>107</v>
-      </c>
-      <c r="G13" t="s">
-        <v>108</v>
       </c>
       <c r="H13" t="s">
         <v>58</v>
       </c>
       <c r="I13" t="s">
+        <v>59</v>
+      </c>
+      <c r="J13" t="s">
+        <v>108</v>
+      </c>
+      <c r="K13" t="s">
         <v>109</v>
-      </c>
-      <c r="J13" t="s">
-        <v>110</v>
-      </c>
-      <c r="K13" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" t="s">
         <v>112</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
         <v>113</v>
       </c>
-      <c r="C14" t="s">
+      <c r="E14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" t="s">
         <v>114</v>
-      </c>
-      <c r="D14" t="s">
-        <v>115</v>
-      </c>
-      <c r="E14" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" t="s">
-        <v>116</v>
-      </c>
-      <c r="G14" t="s">
-        <v>117</v>
       </c>
       <c r="H14" t="s">
         <v>68</v>
       </c>
       <c r="I14" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J14" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K14" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" t="s">
         <v>121</v>
-      </c>
-      <c r="B15" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" t="s">
-        <v>123</v>
-      </c>
-      <c r="D15" t="s">
-        <v>124</v>
       </c>
       <c r="E15" t="s">
         <v>24</v>
@@ -2322,68 +2316,68 @@
         <v>39</v>
       </c>
       <c r="G15" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="H15" t="s">
         <v>77</v>
       </c>
       <c r="I15" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J15" t="s">
         <v>24</v>
       </c>
       <c r="K15" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" t="s">
         <v>128</v>
       </c>
-      <c r="B16" t="s">
+      <c r="G16" t="s">
         <v>129</v>
-      </c>
-      <c r="C16" t="s">
-        <v>130</v>
-      </c>
-      <c r="D16" t="s">
-        <v>131</v>
-      </c>
-      <c r="E16" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" t="s">
-        <v>39</v>
-      </c>
-      <c r="G16" t="s">
-        <v>132</v>
       </c>
       <c r="H16" t="s">
         <v>31</v>
       </c>
       <c r="I16" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J16" t="s">
-        <v>24</v>
+        <v>131</v>
       </c>
       <c r="K16" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" t="s">
         <v>135</v>
       </c>
-      <c r="B17" t="s">
+      <c r="D17" t="s">
         <v>136</v>
-      </c>
-      <c r="C17" t="s">
-        <v>137</v>
-      </c>
-      <c r="D17" t="s">
-        <v>138</v>
       </c>
       <c r="E17" t="s">
         <v>24</v>
@@ -2392,74 +2386,74 @@
         <v>39</v>
       </c>
       <c r="G17" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H17" t="s">
         <v>41</v>
       </c>
       <c r="I17" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J17" t="s">
         <v>24</v>
       </c>
       <c r="K17" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" t="s">
         <v>142</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
         <v>143</v>
       </c>
-      <c r="C18" t="s">
+      <c r="E18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" t="s">
         <v>144</v>
       </c>
-      <c r="D18" t="s">
+      <c r="G18" t="s">
         <v>145</v>
-      </c>
-      <c r="E18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" t="s">
-        <v>116</v>
-      </c>
-      <c r="G18" t="s">
-        <v>146</v>
       </c>
       <c r="H18" t="s">
         <v>49</v>
       </c>
       <c r="I18" t="s">
+        <v>146</v>
+      </c>
+      <c r="J18" t="s">
         <v>147</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>148</v>
-      </c>
-      <c r="K18" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B19" t="s">
         <v>150</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>151</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>152</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" t="s">
         <v>153</v>
-      </c>
-      <c r="E19" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" t="s">
-        <v>116</v>
       </c>
       <c r="G19" t="s">
         <v>154</v>
@@ -2494,36 +2488,36 @@
         <v>24</v>
       </c>
       <c r="F20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G20" t="s">
         <v>162</v>
-      </c>
-      <c r="G20" t="s">
-        <v>163</v>
       </c>
       <c r="H20" t="s">
         <v>68</v>
       </c>
       <c r="I20" t="s">
+        <v>163</v>
+      </c>
+      <c r="J20" t="s">
         <v>164</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>165</v>
-      </c>
-      <c r="K20" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>166</v>
+      </c>
+      <c r="B21" t="s">
         <v>167</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>168</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>169</v>
-      </c>
-      <c r="D21" t="s">
-        <v>170</v>
       </c>
       <c r="E21" t="s">
         <v>24</v>
@@ -2532,33 +2526,33 @@
         <v>39</v>
       </c>
       <c r="G21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H21" t="s">
         <v>77</v>
       </c>
       <c r="I21" t="s">
+        <v>171</v>
+      </c>
+      <c r="J21" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" t="s">
         <v>172</v>
-      </c>
-      <c r="J21" t="s">
-        <v>24</v>
-      </c>
-      <c r="K21" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>173</v>
+      </c>
+      <c r="B22" t="s">
         <v>174</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>175</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>176</v>
-      </c>
-      <c r="D22" t="s">
-        <v>177</v>
       </c>
       <c r="E22" t="s">
         <v>24</v>
@@ -2567,48 +2561,48 @@
         <v>39</v>
       </c>
       <c r="G22" t="s">
+        <v>177</v>
+      </c>
+      <c r="H22" t="s">
         <v>178</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>179</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
+        <v>24</v>
+      </c>
+      <c r="K22" t="s">
         <v>180</v>
-      </c>
-      <c r="J22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K22" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>181</v>
+      </c>
+      <c r="B23" t="s">
         <v>182</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>183</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>184</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>185</v>
-      </c>
-      <c r="E23" t="s">
-        <v>186</v>
       </c>
       <c r="F23" t="s">
         <v>39</v>
       </c>
       <c r="G23" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H23" t="s">
         <v>41</v>
       </c>
       <c r="I23" t="s">
-        <v>33</v>
+        <v>187</v>
       </c>
       <c r="J23" t="s">
         <v>24</v>
@@ -2704,71 +2698,71 @@
         <v>24</v>
       </c>
       <c r="F26" t="s">
-        <v>66</v>
+        <v>211</v>
       </c>
       <c r="G26" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H26" t="s">
         <v>68</v>
       </c>
       <c r="I26" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J26" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K26" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B27" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C27" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D27" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E27" t="s">
         <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G27" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H27" t="s">
         <v>77</v>
       </c>
       <c r="I27" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K27" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B28" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C28" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D28" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E28" t="s">
         <v>24</v>
@@ -2777,103 +2771,103 @@
         <v>39</v>
       </c>
       <c r="G28" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H28" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I28" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J28" t="s">
         <v>24</v>
       </c>
       <c r="K28" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B29" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C29" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D29" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E29" t="s">
         <v>24</v>
       </c>
       <c r="F29" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G29" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H29" t="s">
         <v>41</v>
       </c>
       <c r="I29" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J29" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K29" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B30" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C30" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D30" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E30" t="s">
         <v>24</v>
       </c>
       <c r="F30" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G30" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H30" t="s">
         <v>194</v>
       </c>
       <c r="I30" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J30" t="s">
-        <v>172</v>
+        <v>248</v>
       </c>
       <c r="K30" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B31" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C31" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D31" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E31" t="s">
         <v>24</v>
@@ -2882,33 +2876,33 @@
         <v>39</v>
       </c>
       <c r="G31" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H31" t="s">
         <v>203</v>
       </c>
       <c r="I31" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="J31" t="s">
         <v>24</v>
       </c>
       <c r="K31" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B32" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C32" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D32" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E32" t="s">
         <v>24</v>
@@ -2917,33 +2911,33 @@
         <v>39</v>
       </c>
       <c r="G32" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H32" t="s">
         <v>68</v>
       </c>
       <c r="I32" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J32" t="s">
         <v>24</v>
       </c>
       <c r="K32" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C33" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D33" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E33" t="s">
         <v>24</v>
@@ -2952,33 +2946,33 @@
         <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H33" t="s">
         <v>77</v>
       </c>
       <c r="I33" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J33" t="s">
         <v>24</v>
       </c>
       <c r="K33" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B34" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C34" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D34" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E34" t="s">
         <v>24</v>
@@ -2987,68 +2981,68 @@
         <v>39</v>
       </c>
       <c r="G34" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H34" t="s">
+        <v>178</v>
+      </c>
+      <c r="I34" t="s">
         <v>179</v>
       </c>
-      <c r="I34" t="s">
-        <v>180</v>
-      </c>
       <c r="J34" t="s">
         <v>24</v>
       </c>
       <c r="K34" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B35" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C35" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D35" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E35" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F35" t="s">
         <v>39</v>
       </c>
       <c r="G35" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H35" t="s">
         <v>41</v>
       </c>
       <c r="I35" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J35" t="s">
         <v>24</v>
       </c>
       <c r="K35" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B36" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C36" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D36" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E36" t="s">
         <v>24</v>
@@ -3057,33 +3051,33 @@
         <v>39</v>
       </c>
       <c r="G36" t="s">
-        <v>286</v>
+        <v>128</v>
       </c>
       <c r="H36" t="s">
         <v>194</v>
       </c>
       <c r="I36" t="s">
+        <v>195</v>
+      </c>
+      <c r="J36" t="s">
+        <v>24</v>
+      </c>
+      <c r="K36" t="s">
         <v>287</v>
-      </c>
-      <c r="J36" t="s">
-        <v>24</v>
-      </c>
-      <c r="K36" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>288</v>
+      </c>
+      <c r="B37" t="s">
         <v>289</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>290</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>291</v>
-      </c>
-      <c r="D37" t="s">
-        <v>292</v>
       </c>
       <c r="E37" t="s">
         <v>24</v>
@@ -3092,33 +3086,33 @@
         <v>39</v>
       </c>
       <c r="G37" t="s">
-        <v>286</v>
+        <v>128</v>
       </c>
       <c r="H37" t="s">
         <v>203</v>
       </c>
       <c r="I37" t="s">
+        <v>204</v>
+      </c>
+      <c r="J37" t="s">
+        <v>292</v>
+      </c>
+      <c r="K37" t="s">
         <v>293</v>
-      </c>
-      <c r="J37" t="s">
-        <v>205</v>
-      </c>
-      <c r="K37" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>294</v>
+      </c>
+      <c r="B38" t="s">
         <v>295</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>296</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>297</v>
-      </c>
-      <c r="D38" t="s">
-        <v>298</v>
       </c>
       <c r="E38" t="s">
         <v>24</v>
@@ -3127,33 +3121,33 @@
         <v>39</v>
       </c>
       <c r="G38" t="s">
-        <v>286</v>
+        <v>128</v>
       </c>
       <c r="H38" t="s">
         <v>68</v>
       </c>
       <c r="I38" t="s">
+        <v>298</v>
+      </c>
+      <c r="J38" t="s">
+        <v>24</v>
+      </c>
+      <c r="K38" t="s">
         <v>299</v>
-      </c>
-      <c r="J38" t="s">
-        <v>24</v>
-      </c>
-      <c r="K38" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>300</v>
+      </c>
+      <c r="B39" t="s">
         <v>301</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>302</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>303</v>
-      </c>
-      <c r="D39" t="s">
-        <v>304</v>
       </c>
       <c r="E39" t="s">
         <v>24</v>
@@ -3162,68 +3156,68 @@
         <v>39</v>
       </c>
       <c r="G39" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H39" t="s">
         <v>77</v>
       </c>
       <c r="I39" t="s">
+        <v>304</v>
+      </c>
+      <c r="J39" t="s">
         <v>305</v>
       </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>306</v>
-      </c>
-      <c r="K39" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>307</v>
+      </c>
+      <c r="B40" t="s">
         <v>308</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>309</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>310</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" t="s">
+        <v>128</v>
+      </c>
+      <c r="G40" t="s">
         <v>311</v>
-      </c>
-      <c r="E40" t="s">
-        <v>24</v>
-      </c>
-      <c r="F40" t="s">
-        <v>312</v>
-      </c>
-      <c r="G40" t="s">
-        <v>100</v>
       </c>
       <c r="H40" t="s">
         <v>31</v>
       </c>
       <c r="I40" t="s">
+        <v>268</v>
+      </c>
+      <c r="J40" t="s">
+        <v>312</v>
+      </c>
+      <c r="K40" t="s">
         <v>313</v>
-      </c>
-      <c r="J40" t="s">
-        <v>314</v>
-      </c>
-      <c r="K40" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>314</v>
+      </c>
+      <c r="B41" t="s">
+        <v>315</v>
+      </c>
+      <c r="C41" t="s">
         <v>316</v>
       </c>
-      <c r="B41" t="s">
+      <c r="D41" t="s">
         <v>317</v>
-      </c>
-      <c r="C41" t="s">
-        <v>318</v>
-      </c>
-      <c r="D41" t="s">
-        <v>319</v>
       </c>
       <c r="E41" t="s">
         <v>24</v>
@@ -3232,42 +3226,42 @@
         <v>39</v>
       </c>
       <c r="G41" t="s">
-        <v>100</v>
+        <v>318</v>
       </c>
       <c r="H41" t="s">
         <v>41</v>
       </c>
       <c r="I41" t="s">
+        <v>319</v>
+      </c>
+      <c r="J41" t="s">
+        <v>24</v>
+      </c>
+      <c r="K41" t="s">
         <v>320</v>
-      </c>
-      <c r="J41" t="s">
-        <v>24</v>
-      </c>
-      <c r="K41" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>321</v>
+      </c>
+      <c r="B42" t="s">
         <v>322</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>323</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>324</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
+        <v>24</v>
+      </c>
+      <c r="F42" t="s">
+        <v>153</v>
+      </c>
+      <c r="G42" t="s">
         <v>325</v>
-      </c>
-      <c r="E42" t="s">
-        <v>24</v>
-      </c>
-      <c r="F42" t="s">
-        <v>162</v>
-      </c>
-      <c r="G42" t="s">
-        <v>171</v>
       </c>
       <c r="H42" t="s">
         <v>326</v>
@@ -3334,7 +3328,7 @@
         <v>24</v>
       </c>
       <c r="F44" t="s">
-        <v>39</v>
+        <v>153</v>
       </c>
       <c r="G44" t="s">
         <v>342</v>
@@ -3346,33 +3340,33 @@
         <v>344</v>
       </c>
       <c r="J44" t="s">
-        <v>24</v>
+        <v>345</v>
       </c>
       <c r="K44" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B45" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C45" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D45" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E45" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F45" t="s">
         <v>39</v>
       </c>
       <c r="G45" t="s">
-        <v>351</v>
+        <v>129</v>
       </c>
       <c r="H45" t="s">
         <v>77</v>
@@ -3384,56 +3378,56 @@
         <v>24</v>
       </c>
       <c r="K45" t="s">
-        <v>134</v>
+        <v>353</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B46" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C46" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D46" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E46" t="s">
         <v>24</v>
       </c>
       <c r="F46" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="G46" t="s">
-        <v>139</v>
+        <v>342</v>
       </c>
       <c r="H46" t="s">
         <v>31</v>
       </c>
       <c r="I46" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J46" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K46" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B47" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C47" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D47" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E47" t="s">
         <v>24</v>
@@ -3442,51 +3436,51 @@
         <v>39</v>
       </c>
       <c r="G47" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H47" t="s">
         <v>41</v>
       </c>
       <c r="I47" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J47" t="s">
         <v>24</v>
       </c>
       <c r="K47" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B48" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C48" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D48" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E48" t="s">
         <v>24</v>
       </c>
       <c r="F48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G48" t="s">
-        <v>370</v>
+        <v>170</v>
       </c>
       <c r="H48" t="s">
         <v>326</v>
       </c>
       <c r="I48" t="s">
+        <v>164</v>
+      </c>
+      <c r="J48" t="s">
         <v>371</v>
-      </c>
-      <c r="J48" t="s">
-        <v>320</v>
       </c>
       <c r="K48" t="s">
         <v>372</v>
@@ -3538,16 +3532,16 @@
         <v>383</v>
       </c>
       <c r="D50" t="s">
+        <v>370</v>
+      </c>
+      <c r="E50" t="s">
+        <v>24</v>
+      </c>
+      <c r="F50" t="s">
         <v>384</v>
       </c>
-      <c r="E50" t="s">
-        <v>24</v>
-      </c>
-      <c r="F50" t="s">
-        <v>39</v>
-      </c>
       <c r="G50" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="H50" t="s">
         <v>343</v>
@@ -3556,10 +3550,10 @@
         <v>385</v>
       </c>
       <c r="J50" t="s">
-        <v>24</v>
+        <v>386</v>
       </c>
       <c r="K50" t="s">
-        <v>386</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51">
@@ -3582,7 +3576,7 @@
         <v>39</v>
       </c>
       <c r="G51" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H51" t="s">
         <v>77</v>
@@ -3617,7 +3611,7 @@
         <v>39</v>
       </c>
       <c r="G52" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H52" t="s">
         <v>31</v>
@@ -3626,94 +3620,94 @@
         <v>398</v>
       </c>
       <c r="J52" t="s">
+        <v>24</v>
+      </c>
+      <c r="K52" t="s">
         <v>399</v>
-      </c>
-      <c r="K52" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>400</v>
+      </c>
+      <c r="B53" t="s">
         <v>401</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>402</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>403</v>
       </c>
-      <c r="D53" t="s">
-        <v>404</v>
-      </c>
       <c r="E53" t="s">
         <v>24</v>
       </c>
       <c r="F53" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G53" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H53" t="s">
         <v>41</v>
       </c>
       <c r="I53" t="s">
+        <v>404</v>
+      </c>
+      <c r="J53" t="s">
         <v>405</v>
       </c>
-      <c r="J53" t="s">
+      <c r="K53" t="s">
         <v>406</v>
-      </c>
-      <c r="K53" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>407</v>
+      </c>
+      <c r="B54" t="s">
         <v>408</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>409</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>410</v>
       </c>
-      <c r="D54" t="s">
-        <v>411</v>
-      </c>
       <c r="E54" t="s">
         <v>24</v>
       </c>
       <c r="F54" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G54" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="H54" t="s">
         <v>326</v>
       </c>
       <c r="I54" t="s">
+        <v>411</v>
+      </c>
+      <c r="J54" t="s">
         <v>412</v>
       </c>
-      <c r="J54" t="s">
+      <c r="K54" t="s">
         <v>413</v>
-      </c>
-      <c r="K54" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>414</v>
+      </c>
+      <c r="B55" t="s">
         <v>415</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>416</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>417</v>
-      </c>
-      <c r="D55" t="s">
-        <v>418</v>
       </c>
       <c r="E55" t="s">
         <v>24</v>
@@ -3722,33 +3716,33 @@
         <v>39</v>
       </c>
       <c r="G55" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="H55" t="s">
         <v>203</v>
       </c>
       <c r="I55" t="s">
+        <v>418</v>
+      </c>
+      <c r="J55" t="s">
+        <v>24</v>
+      </c>
+      <c r="K55" t="s">
         <v>419</v>
-      </c>
-      <c r="J55" t="s">
-        <v>24</v>
-      </c>
-      <c r="K55" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>420</v>
+      </c>
+      <c r="B56" t="s">
         <v>421</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>422</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>423</v>
-      </c>
-      <c r="D56" t="s">
-        <v>424</v>
       </c>
       <c r="E56" t="s">
         <v>24</v>
@@ -3763,27 +3757,27 @@
         <v>343</v>
       </c>
       <c r="I56" t="s">
+        <v>424</v>
+      </c>
+      <c r="J56" t="s">
+        <v>24</v>
+      </c>
+      <c r="K56" t="s">
         <v>425</v>
-      </c>
-      <c r="J56" t="s">
-        <v>24</v>
-      </c>
-      <c r="K56" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>426</v>
+      </c>
+      <c r="B57" t="s">
         <v>427</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>428</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>429</v>
-      </c>
-      <c r="D57" t="s">
-        <v>430</v>
       </c>
       <c r="E57" t="s">
         <v>24</v>
@@ -3792,7 +3786,7 @@
         <v>39</v>
       </c>
       <c r="G57" t="s">
-        <v>312</v>
+        <v>430</v>
       </c>
       <c r="H57" t="s">
         <v>77</v>
@@ -3824,197 +3818,197 @@
         <v>24</v>
       </c>
       <c r="F58" t="s">
+        <v>39</v>
+      </c>
+      <c r="G58" t="s">
         <v>437</v>
-      </c>
-      <c r="G58" t="s">
-        <v>438</v>
       </c>
       <c r="H58" t="s">
         <v>31</v>
       </c>
       <c r="I58" t="s">
-        <v>439</v>
+        <v>130</v>
       </c>
       <c r="J58" t="s">
-        <v>440</v>
+        <v>24</v>
       </c>
       <c r="K58" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>439</v>
+      </c>
+      <c r="B59" t="s">
+        <v>440</v>
+      </c>
+      <c r="C59" t="s">
+        <v>441</v>
+      </c>
+      <c r="D59" t="s">
         <v>442</v>
       </c>
-      <c r="B59" t="s">
+      <c r="E59" t="s">
+        <v>24</v>
+      </c>
+      <c r="F59" t="s">
         <v>443</v>
       </c>
-      <c r="C59" t="s">
+      <c r="G59" t="s">
         <v>444</v>
-      </c>
-      <c r="D59" t="s">
-        <v>445</v>
-      </c>
-      <c r="E59" t="s">
-        <v>24</v>
-      </c>
-      <c r="F59" t="s">
-        <v>446</v>
-      </c>
-      <c r="G59" t="s">
-        <v>447</v>
       </c>
       <c r="H59" t="s">
         <v>41</v>
       </c>
       <c r="I59" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="J59" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="K59" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
+        <v>448</v>
+      </c>
+      <c r="B60" t="s">
+        <v>449</v>
+      </c>
+      <c r="C60" t="s">
+        <v>450</v>
+      </c>
+      <c r="D60" t="s">
         <v>451</v>
       </c>
-      <c r="B60" t="s">
+      <c r="E60" t="s">
+        <v>24</v>
+      </c>
+      <c r="F60" t="s">
+        <v>30</v>
+      </c>
+      <c r="G60" t="s">
         <v>452</v>
-      </c>
-      <c r="C60" t="s">
-        <v>453</v>
-      </c>
-      <c r="D60" t="s">
-        <v>454</v>
-      </c>
-      <c r="E60" t="s">
-        <v>24</v>
-      </c>
-      <c r="F60" t="s">
-        <v>455</v>
-      </c>
-      <c r="G60" t="s">
-        <v>456</v>
       </c>
       <c r="H60" t="s">
         <v>326</v>
       </c>
       <c r="I60" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="J60" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="K60" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>456</v>
+      </c>
+      <c r="B61" t="s">
+        <v>457</v>
+      </c>
+      <c r="C61" t="s">
+        <v>458</v>
+      </c>
+      <c r="D61" t="s">
+        <v>459</v>
+      </c>
+      <c r="E61" t="s">
         <v>460</v>
       </c>
-      <c r="B61" t="s">
+      <c r="F61" t="s">
         <v>461</v>
       </c>
-      <c r="C61" t="s">
+      <c r="G61" t="s">
         <v>462</v>
-      </c>
-      <c r="D61" t="s">
-        <v>463</v>
-      </c>
-      <c r="E61" t="s">
-        <v>464</v>
-      </c>
-      <c r="F61" t="s">
-        <v>465</v>
-      </c>
-      <c r="G61" t="s">
-        <v>466</v>
       </c>
       <c r="H61" t="s">
         <v>58</v>
       </c>
       <c r="I61" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="J61" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="K61" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
+        <v>466</v>
+      </c>
+      <c r="B62" t="s">
+        <v>467</v>
+      </c>
+      <c r="C62" t="s">
+        <v>468</v>
+      </c>
+      <c r="D62" t="s">
+        <v>469</v>
+      </c>
+      <c r="E62" t="s">
+        <v>24</v>
+      </c>
+      <c r="F62" t="s">
         <v>470</v>
       </c>
-      <c r="B62" t="s">
+      <c r="G62" t="s">
         <v>471</v>
-      </c>
-      <c r="C62" t="s">
-        <v>472</v>
-      </c>
-      <c r="D62" t="s">
-        <v>473</v>
-      </c>
-      <c r="E62" t="s">
-        <v>24</v>
-      </c>
-      <c r="F62" t="s">
-        <v>39</v>
-      </c>
-      <c r="G62" t="s">
-        <v>474</v>
       </c>
       <c r="H62" t="s">
         <v>343</v>
       </c>
       <c r="I62" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="J62" t="s">
-        <v>24</v>
+        <v>473</v>
       </c>
       <c r="K62" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>475</v>
+      </c>
+      <c r="B63" t="s">
+        <v>476</v>
+      </c>
+      <c r="C63" t="s">
         <v>477</v>
       </c>
-      <c r="B63" t="s">
+      <c r="D63" t="s">
         <v>478</v>
       </c>
-      <c r="C63" t="s">
+      <c r="E63" t="s">
         <v>479</v>
-      </c>
-      <c r="D63" t="s">
-        <v>480</v>
-      </c>
-      <c r="E63" t="s">
-        <v>481</v>
       </c>
       <c r="F63" t="s">
         <v>39</v>
       </c>
       <c r="G63" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H63" t="s">
         <v>77</v>
       </c>
       <c r="I63" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="J63" t="s">
         <v>24</v>
       </c>
       <c r="K63" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
